--- a/backend/templates/UC-18gsm-250W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-250W-BFQR.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7A8DDD-0A45-408B-9D66-FB277C989CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E870AAB6-61A0-4D02-B52E-3F81CFDE7565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page1" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2007,6 +2010,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2056,6 +2065,12 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2391,18 +2406,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4004,11 +4007,11 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="304">
+      <c r="J4" s="178">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="305"/>
+      <c r="K4" s="179"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="147" t="s">
@@ -4040,104 +4043,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="306">
+      <c r="J5" s="194">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="307"/>
+      <c r="K5" s="195"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="208" t="s">
+      <c r="A6" s="212" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="209"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="192"/>
-      <c r="E6" s="193"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="182"/>
-      <c r="H6" s="183"/>
-      <c r="I6" s="206"/>
-      <c r="J6" s="207"/>
+      <c r="B6" s="213"/>
+      <c r="C6" s="214"/>
+      <c r="D6" s="196"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="185"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="211"/>
       <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="192" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="193"/>
-      <c r="C7" s="193"/>
-      <c r="D7" s="211" t="s">
+      <c r="A7" s="196" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="197"/>
+      <c r="C7" s="197"/>
+      <c r="D7" s="215" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="193"/>
+      <c r="E7" s="197"/>
       <c r="F7" s="177"/>
-      <c r="G7" s="182" t="s">
+      <c r="G7" s="184" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="193"/>
-      <c r="I7" s="182" t="s">
+      <c r="H7" s="197"/>
+      <c r="I7" s="184" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="183"/>
-      <c r="K7" s="199" t="s">
+      <c r="J7" s="185"/>
+      <c r="K7" s="203" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="195"/>
-      <c r="C8" s="195"/>
-      <c r="D8" s="194" t="s">
+      <c r="A8" s="198"/>
+      <c r="B8" s="199"/>
+      <c r="C8" s="199"/>
+      <c r="D8" s="198" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="203" t="s">
+      <c r="E8" s="207" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="204" t="s">
+      <c r="F8" s="208" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="196"/>
-      <c r="H8" s="195"/>
-      <c r="I8" s="196" t="s">
+      <c r="G8" s="200"/>
+      <c r="H8" s="199"/>
+      <c r="I8" s="200" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="204"/>
-      <c r="K8" s="200"/>
+      <c r="J8" s="208"/>
+      <c r="K8" s="204"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="194"/>
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
-      <c r="D9" s="194"/>
+      <c r="A9" s="198"/>
+      <c r="B9" s="199"/>
+      <c r="C9" s="199"/>
+      <c r="D9" s="198"/>
       <c r="E9" s="151"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="195"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="200"/>
+      <c r="H9" s="199"/>
       <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
       <c r="J9" s="58">
-        <v>210</v>
-      </c>
-      <c r="K9" s="200"/>
+        <v>250</v>
+      </c>
+      <c r="K9" s="204"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="194"/>
-      <c r="B10" s="195"/>
-      <c r="C10" s="195"/>
-      <c r="D10" s="202"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="199"/>
+      <c r="D10" s="206"/>
       <c r="E10" s="152"/>
-      <c r="F10" s="205"/>
-      <c r="G10" s="197"/>
-      <c r="H10" s="198"/>
+      <c r="F10" s="209"/>
+      <c r="G10" s="201"/>
+      <c r="H10" s="202"/>
       <c r="I10" s="59" t="s">
         <v>124</v>
       </c>
       <c r="J10" s="60">
-        <v>213</v>
-      </c>
-      <c r="K10" s="201"/>
+        <v>253</v>
+      </c>
+      <c r="K10" s="205"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="120">
@@ -4155,10 +4158,10 @@
       <c r="D11" s="61"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="191"/>
-      <c r="H11" s="191"/>
-      <c r="I11" s="178"/>
-      <c r="J11" s="179"/>
+      <c r="G11" s="193"/>
+      <c r="H11" s="193"/>
+      <c r="I11" s="180"/>
+      <c r="J11" s="181"/>
       <c r="K11" s="62"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4177,10 +4180,10 @@
       <c r="D12" s="63"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="190"/>
-      <c r="H12" s="190"/>
-      <c r="I12" s="180"/>
-      <c r="J12" s="181"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="192"/>
+      <c r="I12" s="182"/>
+      <c r="J12" s="183"/>
       <c r="K12" s="64"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4199,10 +4202,10 @@
       <c r="D13" s="63"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="190"/>
-      <c r="H13" s="190"/>
-      <c r="I13" s="180"/>
-      <c r="J13" s="181"/>
+      <c r="G13" s="192"/>
+      <c r="H13" s="192"/>
+      <c r="I13" s="182"/>
+      <c r="J13" s="183"/>
       <c r="K13" s="64"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4221,10 +4224,10 @@
       <c r="D14" s="63"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="190"/>
-      <c r="H14" s="190"/>
-      <c r="I14" s="180"/>
-      <c r="J14" s="181"/>
+      <c r="G14" s="192"/>
+      <c r="H14" s="192"/>
+      <c r="I14" s="182"/>
+      <c r="J14" s="183"/>
       <c r="K14" s="64"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4243,10 +4246,10 @@
       <c r="D15" s="63"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="190"/>
-      <c r="H15" s="190"/>
-      <c r="I15" s="180"/>
-      <c r="J15" s="181"/>
+      <c r="G15" s="192"/>
+      <c r="H15" s="192"/>
+      <c r="I15" s="182"/>
+      <c r="J15" s="183"/>
       <c r="K15" s="64"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4265,10 +4268,10 @@
       <c r="D16" s="61"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="191"/>
-      <c r="H16" s="191"/>
-      <c r="I16" s="180"/>
-      <c r="J16" s="181"/>
+      <c r="G16" s="193"/>
+      <c r="H16" s="193"/>
+      <c r="I16" s="182"/>
+      <c r="J16" s="183"/>
       <c r="K16" s="62"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4287,10 +4290,10 @@
       <c r="D17" s="63"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="190"/>
-      <c r="H17" s="190"/>
-      <c r="I17" s="180"/>
-      <c r="J17" s="181"/>
+      <c r="G17" s="192"/>
+      <c r="H17" s="192"/>
+      <c r="I17" s="182"/>
+      <c r="J17" s="183"/>
       <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4309,10 +4312,10 @@
       <c r="D18" s="63"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="190"/>
-      <c r="H18" s="190"/>
-      <c r="I18" s="180"/>
-      <c r="J18" s="181"/>
+      <c r="G18" s="192"/>
+      <c r="H18" s="192"/>
+      <c r="I18" s="182"/>
+      <c r="J18" s="183"/>
       <c r="K18" s="64"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4331,10 +4334,10 @@
       <c r="D19" s="63"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="190"/>
-      <c r="H19" s="190"/>
-      <c r="I19" s="180"/>
-      <c r="J19" s="181"/>
+      <c r="G19" s="192"/>
+      <c r="H19" s="192"/>
+      <c r="I19" s="182"/>
+      <c r="J19" s="183"/>
       <c r="K19" s="64"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4353,10 +4356,10 @@
       <c r="D20" s="63"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="186"/>
-      <c r="H20" s="187"/>
-      <c r="I20" s="180"/>
-      <c r="J20" s="181"/>
+      <c r="G20" s="188"/>
+      <c r="H20" s="189"/>
+      <c r="I20" s="182"/>
+      <c r="J20" s="183"/>
       <c r="K20" s="64"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4375,10 +4378,10 @@
       <c r="D21" s="63"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="186"/>
-      <c r="H21" s="187"/>
-      <c r="I21" s="180"/>
-      <c r="J21" s="181"/>
+      <c r="G21" s="188"/>
+      <c r="H21" s="189"/>
+      <c r="I21" s="182"/>
+      <c r="J21" s="183"/>
       <c r="K21" s="64"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4397,10 +4400,10 @@
       <c r="D22" s="63"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="186"/>
-      <c r="H22" s="187"/>
-      <c r="I22" s="180"/>
-      <c r="J22" s="181"/>
+      <c r="G22" s="188"/>
+      <c r="H22" s="189"/>
+      <c r="I22" s="182"/>
+      <c r="J22" s="183"/>
       <c r="K22" s="64"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4419,10 +4422,10 @@
       <c r="D23" s="63"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="186"/>
-      <c r="H23" s="187"/>
-      <c r="I23" s="180"/>
-      <c r="J23" s="181"/>
+      <c r="G23" s="188"/>
+      <c r="H23" s="189"/>
+      <c r="I23" s="182"/>
+      <c r="J23" s="183"/>
       <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4441,10 +4444,10 @@
       <c r="D24" s="63"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="186"/>
-      <c r="H24" s="187"/>
-      <c r="I24" s="180"/>
-      <c r="J24" s="181"/>
+      <c r="G24" s="188"/>
+      <c r="H24" s="189"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="183"/>
       <c r="K24" s="64"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4463,10 +4466,10 @@
       <c r="D25" s="63"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="186"/>
-      <c r="H25" s="187"/>
-      <c r="I25" s="180"/>
-      <c r="J25" s="181"/>
+      <c r="G25" s="188"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="182"/>
+      <c r="J25" s="183"/>
       <c r="K25" s="64"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4485,10 +4488,10 @@
       <c r="D26" s="63"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="186"/>
-      <c r="H26" s="187"/>
-      <c r="I26" s="180"/>
-      <c r="J26" s="181"/>
+      <c r="G26" s="188"/>
+      <c r="H26" s="189"/>
+      <c r="I26" s="182"/>
+      <c r="J26" s="183"/>
       <c r="K26" s="64"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4507,10 +4510,10 @@
       <c r="D27" s="63"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="186"/>
-      <c r="H27" s="187"/>
-      <c r="I27" s="180"/>
-      <c r="J27" s="181"/>
+      <c r="G27" s="188"/>
+      <c r="H27" s="189"/>
+      <c r="I27" s="182"/>
+      <c r="J27" s="183"/>
       <c r="K27" s="64"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4529,10 +4532,10 @@
       <c r="D28" s="63"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="186"/>
-      <c r="H28" s="187"/>
-      <c r="I28" s="180"/>
-      <c r="J28" s="181"/>
+      <c r="G28" s="188"/>
+      <c r="H28" s="189"/>
+      <c r="I28" s="182"/>
+      <c r="J28" s="183"/>
       <c r="K28" s="64"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4551,10 +4554,10 @@
       <c r="D29" s="63"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="186"/>
-      <c r="H29" s="187"/>
-      <c r="I29" s="180"/>
-      <c r="J29" s="181"/>
+      <c r="G29" s="188"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="182"/>
+      <c r="J29" s="183"/>
       <c r="K29" s="64"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4573,10 +4576,10 @@
       <c r="D30" s="63"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="186"/>
-      <c r="H30" s="187"/>
-      <c r="I30" s="180"/>
-      <c r="J30" s="181"/>
+      <c r="G30" s="188"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="182"/>
+      <c r="J30" s="183"/>
       <c r="K30" s="64"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4595,10 +4598,10 @@
       <c r="D31" s="63"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="186"/>
-      <c r="H31" s="187"/>
-      <c r="I31" s="180"/>
-      <c r="J31" s="181"/>
+      <c r="G31" s="188"/>
+      <c r="H31" s="189"/>
+      <c r="I31" s="182"/>
+      <c r="J31" s="183"/>
       <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4617,10 +4620,10 @@
       <c r="D32" s="63"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="186"/>
-      <c r="H32" s="187"/>
-      <c r="I32" s="180"/>
-      <c r="J32" s="181"/>
+      <c r="G32" s="188"/>
+      <c r="H32" s="189"/>
+      <c r="I32" s="182"/>
+      <c r="J32" s="183"/>
       <c r="K32" s="64"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4639,10 +4642,10 @@
       <c r="D33" s="63"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="186"/>
-      <c r="H33" s="187"/>
-      <c r="I33" s="180"/>
-      <c r="J33" s="181"/>
+      <c r="G33" s="188"/>
+      <c r="H33" s="189"/>
+      <c r="I33" s="182"/>
+      <c r="J33" s="183"/>
       <c r="K33" s="64"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4661,10 +4664,10 @@
       <c r="D34" s="63"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="186"/>
-      <c r="H34" s="187"/>
-      <c r="I34" s="180"/>
-      <c r="J34" s="181"/>
+      <c r="G34" s="188"/>
+      <c r="H34" s="189"/>
+      <c r="I34" s="182"/>
+      <c r="J34" s="183"/>
       <c r="K34" s="64"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4683,10 +4686,10 @@
       <c r="D35" s="63"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="186"/>
-      <c r="H35" s="187"/>
-      <c r="I35" s="180"/>
-      <c r="J35" s="181"/>
+      <c r="G35" s="188"/>
+      <c r="H35" s="189"/>
+      <c r="I35" s="182"/>
+      <c r="J35" s="183"/>
       <c r="K35" s="64"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4705,10 +4708,10 @@
       <c r="D36" s="63"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="186"/>
-      <c r="H36" s="187"/>
-      <c r="I36" s="180"/>
-      <c r="J36" s="181"/>
+      <c r="G36" s="188"/>
+      <c r="H36" s="189"/>
+      <c r="I36" s="182"/>
+      <c r="J36" s="183"/>
       <c r="K36" s="64"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4727,10 +4730,10 @@
       <c r="D37" s="63"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="186"/>
-      <c r="H37" s="187"/>
-      <c r="I37" s="180"/>
-      <c r="J37" s="181"/>
+      <c r="G37" s="188"/>
+      <c r="H37" s="189"/>
+      <c r="I37" s="182"/>
+      <c r="J37" s="183"/>
       <c r="K37" s="64"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4749,10 +4752,10 @@
       <c r="D38" s="63"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="186"/>
-      <c r="H38" s="187"/>
-      <c r="I38" s="180"/>
-      <c r="J38" s="181"/>
+      <c r="G38" s="188"/>
+      <c r="H38" s="189"/>
+      <c r="I38" s="182"/>
+      <c r="J38" s="183"/>
       <c r="K38" s="64"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4771,10 +4774,10 @@
       <c r="D39" s="63"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="186"/>
-      <c r="H39" s="187"/>
-      <c r="I39" s="180"/>
-      <c r="J39" s="181"/>
+      <c r="G39" s="188"/>
+      <c r="H39" s="189"/>
+      <c r="I39" s="182"/>
+      <c r="J39" s="183"/>
       <c r="K39" s="64"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4793,10 +4796,10 @@
       <c r="D40" s="63"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="190"/>
-      <c r="H40" s="190"/>
-      <c r="I40" s="180"/>
-      <c r="J40" s="181"/>
+      <c r="G40" s="192"/>
+      <c r="H40" s="192"/>
+      <c r="I40" s="182"/>
+      <c r="J40" s="183"/>
       <c r="K40" s="64"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4817,16 +4820,16 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="188" t="e">
+      <c r="G41" s="190" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="189"/>
-      <c r="I41" s="220" t="e">
+      <c r="H41" s="191"/>
+      <c r="I41" s="224" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="221"/>
+      <c r="J41" s="225"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
@@ -4850,27 +4853,27 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="184">
+      <c r="G42" s="186">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="185"/>
-      <c r="I42" s="218">
+      <c r="H42" s="187"/>
+      <c r="I42" s="222">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="219"/>
+      <c r="J42" s="223"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="216" t="s">
+      <c r="A43" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="217"/>
-      <c r="C43" s="217"/>
+      <c r="B43" s="221"/>
+      <c r="C43" s="221"/>
       <c r="D43" s="67">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4883,16 +4886,16 @@
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="212">
+      <c r="G43" s="216">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="213"/>
-      <c r="I43" s="214">
+      <c r="H43" s="217"/>
+      <c r="I43" s="218">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="215"/>
+      <c r="J43" s="219"/>
       <c r="K43" s="69">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -5233,11 +5236,11 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="304">
+      <c r="J4" s="178">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="305"/>
+      <c r="K4" s="179"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="147" t="s">
@@ -5269,79 +5272,79 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="306">
+      <c r="J5" s="194">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="307"/>
+      <c r="K5" s="195"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="225" t="s">
+      <c r="A6" s="229" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="226"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="228"/>
+      <c r="B6" s="230"/>
+      <c r="C6" s="231"/>
+      <c r="D6" s="232"/>
       <c r="E6" s="134"/>
       <c r="F6" s="134"/>
       <c r="G6" s="154"/>
       <c r="H6" s="71"/>
-      <c r="I6" s="192"/>
-      <c r="J6" s="193"/>
-      <c r="K6" s="199"/>
+      <c r="I6" s="196"/>
+      <c r="J6" s="197"/>
+      <c r="K6" s="203"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="192" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="193"/>
-      <c r="C7" s="193"/>
-      <c r="D7" s="211" t="s">
+      <c r="A7" s="196" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="197"/>
+      <c r="C7" s="197"/>
+      <c r="D7" s="215" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="229"/>
-      <c r="F7" s="229"/>
+      <c r="E7" s="233"/>
+      <c r="F7" s="233"/>
       <c r="G7" s="177"/>
-      <c r="H7" s="222" t="s">
+      <c r="H7" s="226" t="s">
         <v>126</v>
       </c>
-      <c r="I7" s="194"/>
-      <c r="J7" s="195"/>
-      <c r="K7" s="200"/>
+      <c r="I7" s="198"/>
+      <c r="J7" s="199"/>
+      <c r="K7" s="204"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="194"/>
-      <c r="B8" s="195"/>
-      <c r="C8" s="195"/>
-      <c r="D8" s="232" t="s">
+      <c r="A8" s="198"/>
+      <c r="B8" s="199"/>
+      <c r="C8" s="199"/>
+      <c r="D8" s="236" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="203" t="s">
+      <c r="E8" s="207" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="203" t="s">
+      <c r="F8" s="207" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="203" t="s">
+      <c r="G8" s="207" t="s">
         <v>128</v>
       </c>
-      <c r="H8" s="223"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="195"/>
-      <c r="K8" s="200"/>
+      <c r="H8" s="227"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="199"/>
+      <c r="K8" s="204"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="194"/>
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
-      <c r="D9" s="233"/>
+      <c r="A9" s="198"/>
+      <c r="B9" s="199"/>
+      <c r="C9" s="199"/>
+      <c r="D9" s="237"/>
       <c r="E9" s="152"/>
       <c r="F9" s="152"/>
       <c r="G9" s="152"/>
-      <c r="H9" s="224"/>
-      <c r="I9" s="194"/>
-      <c r="J9" s="195"/>
-      <c r="K9" s="200"/>
+      <c r="H9" s="228"/>
+      <c r="I9" s="198"/>
+      <c r="J9" s="199"/>
+      <c r="K9" s="204"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="120">
@@ -5361,9 +5364,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="73"/>
       <c r="H10" s="74"/>
-      <c r="I10" s="194"/>
-      <c r="J10" s="195"/>
-      <c r="K10" s="200"/>
+      <c r="I10" s="198"/>
+      <c r="J10" s="199"/>
+      <c r="K10" s="204"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="123">
@@ -5383,9 +5386,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="76"/>
       <c r="H11" s="77"/>
-      <c r="I11" s="194"/>
-      <c r="J11" s="195"/>
-      <c r="K11" s="200"/>
+      <c r="I11" s="198"/>
+      <c r="J11" s="199"/>
+      <c r="K11" s="204"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="123">
@@ -5405,9 +5408,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="76"/>
       <c r="H12" s="77"/>
-      <c r="I12" s="194"/>
-      <c r="J12" s="195"/>
-      <c r="K12" s="200"/>
+      <c r="I12" s="198"/>
+      <c r="J12" s="199"/>
+      <c r="K12" s="204"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="123">
@@ -5427,9 +5430,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="73"/>
       <c r="H13" s="77"/>
-      <c r="I13" s="194"/>
-      <c r="J13" s="195"/>
-      <c r="K13" s="200"/>
+      <c r="I13" s="198"/>
+      <c r="J13" s="199"/>
+      <c r="K13" s="204"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="123">
@@ -5449,9 +5452,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="76"/>
       <c r="H14" s="77"/>
-      <c r="I14" s="194"/>
-      <c r="J14" s="195"/>
-      <c r="K14" s="200"/>
+      <c r="I14" s="198"/>
+      <c r="J14" s="199"/>
+      <c r="K14" s="204"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="123">
@@ -5471,9 +5474,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="76"/>
       <c r="H15" s="77"/>
-      <c r="I15" s="194"/>
-      <c r="J15" s="195"/>
-      <c r="K15" s="200"/>
+      <c r="I15" s="198"/>
+      <c r="J15" s="199"/>
+      <c r="K15" s="204"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="123">
@@ -5493,9 +5496,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="76"/>
       <c r="H16" s="77"/>
-      <c r="I16" s="194"/>
-      <c r="J16" s="195"/>
-      <c r="K16" s="200"/>
+      <c r="I16" s="198"/>
+      <c r="J16" s="199"/>
+      <c r="K16" s="204"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="123">
@@ -5515,9 +5518,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="76"/>
       <c r="H17" s="77"/>
-      <c r="I17" s="194"/>
-      <c r="J17" s="195"/>
-      <c r="K17" s="200"/>
+      <c r="I17" s="198"/>
+      <c r="J17" s="199"/>
+      <c r="K17" s="204"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="123">
@@ -5537,9 +5540,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="76"/>
       <c r="H18" s="77"/>
-      <c r="I18" s="194"/>
-      <c r="J18" s="195"/>
-      <c r="K18" s="200"/>
+      <c r="I18" s="198"/>
+      <c r="J18" s="199"/>
+      <c r="K18" s="204"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="123">
@@ -5559,9 +5562,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="76"/>
       <c r="H19" s="77"/>
-      <c r="I19" s="194"/>
-      <c r="J19" s="195"/>
-      <c r="K19" s="200"/>
+      <c r="I19" s="198"/>
+      <c r="J19" s="199"/>
+      <c r="K19" s="204"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
@@ -5581,9 +5584,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="76"/>
       <c r="H20" s="77"/>
-      <c r="I20" s="194"/>
-      <c r="J20" s="195"/>
-      <c r="K20" s="200"/>
+      <c r="I20" s="198"/>
+      <c r="J20" s="199"/>
+      <c r="K20" s="204"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="123">
@@ -5603,9 +5606,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="76"/>
       <c r="H21" s="77"/>
-      <c r="I21" s="194"/>
-      <c r="J21" s="195"/>
-      <c r="K21" s="200"/>
+      <c r="I21" s="198"/>
+      <c r="J21" s="199"/>
+      <c r="K21" s="204"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="123">
@@ -5625,9 +5628,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="76"/>
       <c r="H22" s="77"/>
-      <c r="I22" s="194"/>
-      <c r="J22" s="195"/>
-      <c r="K22" s="200"/>
+      <c r="I22" s="198"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="204"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="123">
@@ -5647,9 +5650,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="76"/>
       <c r="H23" s="77"/>
-      <c r="I23" s="194"/>
-      <c r="J23" s="195"/>
-      <c r="K23" s="200"/>
+      <c r="I23" s="198"/>
+      <c r="J23" s="199"/>
+      <c r="K23" s="204"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="123">
@@ -5669,9 +5672,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="76"/>
       <c r="H24" s="77"/>
-      <c r="I24" s="194"/>
-      <c r="J24" s="195"/>
-      <c r="K24" s="200"/>
+      <c r="I24" s="198"/>
+      <c r="J24" s="199"/>
+      <c r="K24" s="204"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="123">
@@ -5691,9 +5694,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="76"/>
       <c r="H25" s="77"/>
-      <c r="I25" s="194"/>
-      <c r="J25" s="195"/>
-      <c r="K25" s="200"/>
+      <c r="I25" s="198"/>
+      <c r="J25" s="199"/>
+      <c r="K25" s="204"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="123">
@@ -5713,9 +5716,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="76"/>
       <c r="H26" s="77"/>
-      <c r="I26" s="194"/>
-      <c r="J26" s="195"/>
-      <c r="K26" s="200"/>
+      <c r="I26" s="198"/>
+      <c r="J26" s="199"/>
+      <c r="K26" s="204"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="123">
@@ -5735,9 +5738,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="76"/>
       <c r="H27" s="77"/>
-      <c r="I27" s="194"/>
-      <c r="J27" s="195"/>
-      <c r="K27" s="200"/>
+      <c r="I27" s="198"/>
+      <c r="J27" s="199"/>
+      <c r="K27" s="204"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="123">
@@ -5757,9 +5760,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="76"/>
       <c r="H28" s="77"/>
-      <c r="I28" s="194"/>
-      <c r="J28" s="195"/>
-      <c r="K28" s="200"/>
+      <c r="I28" s="198"/>
+      <c r="J28" s="199"/>
+      <c r="K28" s="204"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="123">
@@ -5779,9 +5782,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="76"/>
       <c r="H29" s="77"/>
-      <c r="I29" s="194"/>
-      <c r="J29" s="195"/>
-      <c r="K29" s="200"/>
+      <c r="I29" s="198"/>
+      <c r="J29" s="199"/>
+      <c r="K29" s="204"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
@@ -5801,9 +5804,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="76"/>
       <c r="H30" s="77"/>
-      <c r="I30" s="194"/>
-      <c r="J30" s="195"/>
-      <c r="K30" s="200"/>
+      <c r="I30" s="198"/>
+      <c r="J30" s="199"/>
+      <c r="K30" s="204"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="123">
@@ -5823,9 +5826,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="76"/>
       <c r="H31" s="77"/>
-      <c r="I31" s="194"/>
-      <c r="J31" s="195"/>
-      <c r="K31" s="200"/>
+      <c r="I31" s="198"/>
+      <c r="J31" s="199"/>
+      <c r="K31" s="204"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="123">
@@ -5845,9 +5848,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="76"/>
       <c r="H32" s="77"/>
-      <c r="I32" s="194"/>
-      <c r="J32" s="195"/>
-      <c r="K32" s="200"/>
+      <c r="I32" s="198"/>
+      <c r="J32" s="199"/>
+      <c r="K32" s="204"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="123">
@@ -5867,9 +5870,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="76"/>
       <c r="H33" s="77"/>
-      <c r="I33" s="194"/>
-      <c r="J33" s="195"/>
-      <c r="K33" s="200"/>
+      <c r="I33" s="198"/>
+      <c r="J33" s="199"/>
+      <c r="K33" s="204"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="123">
@@ -5889,9 +5892,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="76"/>
       <c r="H34" s="77"/>
-      <c r="I34" s="194"/>
-      <c r="J34" s="195"/>
-      <c r="K34" s="200"/>
+      <c r="I34" s="198"/>
+      <c r="J34" s="199"/>
+      <c r="K34" s="204"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="123">
@@ -5911,9 +5914,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="76"/>
       <c r="H35" s="77"/>
-      <c r="I35" s="194"/>
-      <c r="J35" s="195"/>
-      <c r="K35" s="200"/>
+      <c r="I35" s="198"/>
+      <c r="J35" s="199"/>
+      <c r="K35" s="204"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="123">
@@ -5933,9 +5936,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="76"/>
       <c r="H36" s="77"/>
-      <c r="I36" s="194"/>
-      <c r="J36" s="195"/>
-      <c r="K36" s="200"/>
+      <c r="I36" s="198"/>
+      <c r="J36" s="199"/>
+      <c r="K36" s="204"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="123">
@@ -5955,9 +5958,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="76"/>
       <c r="H37" s="77"/>
-      <c r="I37" s="194"/>
-      <c r="J37" s="195"/>
-      <c r="K37" s="200"/>
+      <c r="I37" s="198"/>
+      <c r="J37" s="199"/>
+      <c r="K37" s="204"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="123">
@@ -5977,9 +5980,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="76"/>
       <c r="H38" s="77"/>
-      <c r="I38" s="194"/>
-      <c r="J38" s="195"/>
-      <c r="K38" s="200"/>
+      <c r="I38" s="198"/>
+      <c r="J38" s="199"/>
+      <c r="K38" s="204"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="130">
@@ -5999,16 +6002,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="76"/>
       <c r="H39" s="77"/>
-      <c r="I39" s="194"/>
-      <c r="J39" s="195"/>
-      <c r="K39" s="200"/>
+      <c r="I39" s="198"/>
+      <c r="J39" s="199"/>
+      <c r="K39" s="204"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="230" t="s">
+      <c r="A40" s="234" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="231"/>
-      <c r="C40" s="231"/>
+      <c r="B40" s="235"/>
+      <c r="C40" s="235"/>
       <c r="D40" s="78" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -6029,9 +6032,9 @@
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="195"/>
-      <c r="J40" s="195"/>
-      <c r="K40" s="200"/>
+      <c r="I40" s="199"/>
+      <c r="J40" s="199"/>
+      <c r="K40" s="204"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="174" t="s">
@@ -6059,16 +6062,16 @@
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="195"/>
-      <c r="J41" s="195"/>
-      <c r="K41" s="200"/>
+      <c r="I41" s="199"/>
+      <c r="J41" s="199"/>
+      <c r="K41" s="204"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="216" t="s">
+      <c r="A42" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="217"/>
-      <c r="C42" s="217"/>
+      <c r="B42" s="221"/>
+      <c r="C42" s="221"/>
       <c r="D42" s="82">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -6089,9 +6092,9 @@
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="198"/>
-      <c r="J42" s="198"/>
-      <c r="K42" s="201"/>
+      <c r="I42" s="202"/>
+      <c r="J42" s="202"/>
+      <c r="K42" s="205"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
@@ -6242,15 +6245,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="288" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="G1" s="286"/>
+      <c r="B1" s="289"/>
+      <c r="C1" s="289"/>
+      <c r="D1" s="289"/>
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="290"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -6264,37 +6267,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="292" t="s">
+      <c r="A3" s="296" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="293"/>
-      <c r="C3" s="293"/>
-      <c r="D3" s="293"/>
-      <c r="E3" s="293"/>
-      <c r="F3" s="293"/>
-      <c r="G3" s="294"/>
+      <c r="B3" s="297"/>
+      <c r="C3" s="297"/>
+      <c r="D3" s="297"/>
+      <c r="E3" s="297"/>
+      <c r="F3" s="297"/>
+      <c r="G3" s="298"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="194" t="s">
+      <c r="A4" s="198" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="200"/>
+      <c r="B4" s="199"/>
+      <c r="C4" s="199"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="199"/>
+      <c r="F4" s="199"/>
+      <c r="G4" s="204"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="287" t="s">
+      <c r="A5" s="291" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="288"/>
-      <c r="C5" s="288"/>
-      <c r="D5" s="288"/>
-      <c r="E5" s="288"/>
-      <c r="F5" s="288"/>
-      <c r="G5" s="289"/>
+      <c r="B5" s="292"/>
+      <c r="C5" s="292"/>
+      <c r="D5" s="292"/>
+      <c r="E5" s="292"/>
+      <c r="F5" s="292"/>
+      <c r="G5" s="293"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -6306,14 +6309,14 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="252" t="s">
+      <c r="D6" s="256" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="254"/>
-      <c r="F6" s="290" t="s">
+      <c r="E6" s="258"/>
+      <c r="F6" s="294" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="275">
+      <c r="G6" s="279">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6326,13 +6329,13 @@
       <c r="C7" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="252">
+      <c r="D7" s="256">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="254"/>
-      <c r="F7" s="290"/>
-      <c r="G7" s="291"/>
+      <c r="E7" s="258"/>
+      <c r="F7" s="294"/>
+      <c r="G7" s="295"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -6345,15 +6348,15 @@
       <c r="C8" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="294">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="290"/>
-      <c r="F8" s="272" t="s">
+      <c r="E8" s="294"/>
+      <c r="F8" s="276" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="275">
+      <c r="G8" s="279">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6366,15 +6369,15 @@
         <f>Page1!G44</f>
         <v>461309100</v>
       </c>
-      <c r="C9" s="272" t="s">
+      <c r="C9" s="276" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="278" t="s">
+      <c r="D9" s="282" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="279"/>
-      <c r="F9" s="273"/>
-      <c r="G9" s="276"/>
+      <c r="E9" s="283"/>
+      <c r="F9" s="277"/>
+      <c r="G9" s="280"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -6384,34 +6387,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="274"/>
-      <c r="D10" s="280"/>
-      <c r="E10" s="281"/>
-      <c r="F10" s="274"/>
-      <c r="G10" s="277"/>
+      <c r="C10" s="278"/>
+      <c r="D10" s="284"/>
+      <c r="E10" s="285"/>
+      <c r="F10" s="278"/>
+      <c r="G10" s="281"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="295" t="s">
+      <c r="A11" s="299" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="297" t="s">
+      <c r="B11" s="301" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="299" t="s">
+      <c r="C11" s="303" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="300"/>
-      <c r="E11" s="301"/>
-      <c r="F11" s="297" t="s">
+      <c r="D11" s="304"/>
+      <c r="E11" s="305"/>
+      <c r="F11" s="301" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="302" t="s">
+      <c r="G11" s="306" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="296"/>
-      <c r="B12" s="298"/>
+      <c r="A12" s="300"/>
+      <c r="B12" s="302"/>
       <c r="C12" s="99" t="s">
         <v>60</v>
       </c>
@@ -6421,8 +6424,8 @@
       <c r="E12" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="298"/>
-      <c r="G12" s="303"/>
+      <c r="F12" s="302"/>
+      <c r="G12" s="307"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -6492,7 +6495,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="282" t="s">
+      <c r="G15" s="286" t="s">
         <v>71</v>
       </c>
     </row>
@@ -6516,7 +6519,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="223"/>
+      <c r="G16" s="227"/>
     </row>
     <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
@@ -6538,7 +6541,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="223"/>
+      <c r="G17" s="227"/>
     </row>
     <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104" t="s">
@@ -6560,7 +6563,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="223"/>
+      <c r="G18" s="227"/>
     </row>
     <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104" t="s">
@@ -6582,7 +6585,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="223"/>
+      <c r="G19" s="227"/>
     </row>
     <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
@@ -6604,7 +6607,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="223"/>
+      <c r="G20" s="227"/>
     </row>
     <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
@@ -6626,7 +6629,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="223"/>
+      <c r="G21" s="227"/>
     </row>
     <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="104" t="s">
@@ -6690,7 +6693,7 @@
       </c>
       <c r="E24" s="39">
         <f>Page2!J10</f>
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="F24" s="39" t="e">
         <f>Page2!I41</f>
@@ -6748,26 +6751,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="266" t="s">
+      <c r="A27" s="270" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="267"/>
-      <c r="C27" s="267"/>
-      <c r="D27" s="267"/>
-      <c r="E27" s="267"/>
-      <c r="F27" s="267"/>
-      <c r="G27" s="268"/>
+      <c r="B27" s="271"/>
+      <c r="C27" s="271"/>
+      <c r="D27" s="271"/>
+      <c r="E27" s="271"/>
+      <c r="F27" s="271"/>
+      <c r="G27" s="272"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="250" t="s">
+      <c r="A28" s="254" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="251"/>
-      <c r="C28" s="269" t="s">
+      <c r="B28" s="255"/>
+      <c r="C28" s="273" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="270"/>
-      <c r="E28" s="271"/>
+      <c r="D28" s="274"/>
+      <c r="E28" s="275"/>
       <c r="F28" s="113" t="s">
         <v>92</v>
       </c>
@@ -6776,15 +6779,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="255" t="s">
+      <c r="A29" s="259" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="254"/>
-      <c r="C29" s="260" t="s">
+      <c r="B29" s="258"/>
+      <c r="C29" s="264" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="261"/>
-      <c r="E29" s="262"/>
+      <c r="D29" s="265"/>
+      <c r="E29" s="266"/>
       <c r="F29" s="66" t="s">
         <v>92</v>
       </c>
@@ -6793,15 +6796,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="255" t="s">
+      <c r="A30" s="259" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="254"/>
-      <c r="C30" s="260" t="s">
+      <c r="B30" s="258"/>
+      <c r="C30" s="264" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="261"/>
-      <c r="E30" s="262"/>
+      <c r="D30" s="265"/>
+      <c r="E30" s="266"/>
       <c r="F30" s="66" t="s">
         <v>92</v>
       </c>
@@ -6810,15 +6813,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="255" t="s">
+      <c r="A31" s="259" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="254"/>
-      <c r="C31" s="260" t="s">
+      <c r="B31" s="258"/>
+      <c r="C31" s="264" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="261"/>
-      <c r="E31" s="262"/>
+      <c r="D31" s="265"/>
+      <c r="E31" s="266"/>
       <c r="F31" s="66" t="s">
         <v>92</v>
       </c>
@@ -6827,15 +6830,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="255" t="s">
+      <c r="A32" s="259" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="254"/>
-      <c r="C32" s="260" t="s">
+      <c r="B32" s="258"/>
+      <c r="C32" s="264" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="261"/>
-      <c r="E32" s="262"/>
+      <c r="D32" s="265"/>
+      <c r="E32" s="266"/>
       <c r="F32" s="66" t="s">
         <v>92</v>
       </c>
@@ -6844,15 +6847,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="255" t="s">
+      <c r="A33" s="259" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="254"/>
-      <c r="C33" s="260" t="s">
+      <c r="B33" s="258"/>
+      <c r="C33" s="264" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="261"/>
-      <c r="E33" s="262"/>
+      <c r="D33" s="265"/>
+      <c r="E33" s="266"/>
       <c r="F33" s="66" t="s">
         <v>92</v>
       </c>
@@ -6865,11 +6868,11 @@
         <v>105</v>
       </c>
       <c r="B34" s="148"/>
-      <c r="C34" s="263" t="s">
+      <c r="C34" s="267" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="264"/>
-      <c r="E34" s="265"/>
+      <c r="D34" s="268"/>
+      <c r="E34" s="269"/>
       <c r="F34" s="114" t="s">
         <v>92</v>
       </c>
@@ -6878,25 +6881,25 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="266" t="s">
+      <c r="A35" s="270" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="267"/>
-      <c r="C35" s="267"/>
-      <c r="D35" s="267"/>
-      <c r="E35" s="267"/>
-      <c r="F35" s="267"/>
-      <c r="G35" s="268"/>
+      <c r="B35" s="271"/>
+      <c r="C35" s="271"/>
+      <c r="D35" s="271"/>
+      <c r="E35" s="271"/>
+      <c r="F35" s="271"/>
+      <c r="G35" s="272"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="143" t="s">
         <v>108</v>
       </c>
       <c r="B36" s="144"/>
-      <c r="C36" s="258" t="s">
+      <c r="C36" s="262" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="259"/>
+      <c r="D36" s="263"/>
       <c r="E36" s="144"/>
       <c r="F36" s="10" t="s">
         <v>92</v>
@@ -6906,15 +6909,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="250" t="s">
+      <c r="A37" s="254" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="251"/>
-      <c r="C37" s="252" t="s">
+      <c r="B37" s="255"/>
+      <c r="C37" s="256" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="253"/>
-      <c r="E37" s="254"/>
+      <c r="D37" s="257"/>
+      <c r="E37" s="258"/>
       <c r="F37" s="106" t="s">
         <v>92</v>
       </c>
@@ -6923,15 +6926,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="255" t="s">
+      <c r="A38" s="259" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="254"/>
-      <c r="C38" s="252" t="s">
+      <c r="B38" s="258"/>
+      <c r="C38" s="256" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="253"/>
-      <c r="E38" s="254"/>
+      <c r="D38" s="257"/>
+      <c r="E38" s="258"/>
       <c r="F38" s="106" t="s">
         <v>92</v>
       </c>
@@ -6944,10 +6947,10 @@
         <v>113</v>
       </c>
       <c r="B39" s="148"/>
-      <c r="C39" s="256" t="s">
+      <c r="C39" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="257"/>
+      <c r="D39" s="261"/>
       <c r="E39" s="148"/>
       <c r="F39" s="1" t="s">
         <v>92</v>
@@ -6957,50 +6960,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="236" t="s">
+      <c r="A40" s="240" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="237"/>
-      <c r="C40" s="238" t="s">
+      <c r="B40" s="241"/>
+      <c r="C40" s="242" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="240"/>
-      <c r="F40" s="238" t="s">
+      <c r="D40" s="243"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="242" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="240"/>
+      <c r="G40" s="244"/>
     </row>
     <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="241"/>
-      <c r="B41" s="242"/>
-      <c r="C41" s="194"/>
-      <c r="D41" s="195"/>
-      <c r="E41" s="200"/>
-      <c r="F41" s="245"/>
-      <c r="G41" s="246"/>
+      <c r="A41" s="245"/>
+      <c r="B41" s="246"/>
+      <c r="C41" s="198"/>
+      <c r="D41" s="199"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="249"/>
+      <c r="G41" s="250"/>
     </row>
     <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="243"/>
-      <c r="B42" s="244"/>
-      <c r="C42" s="247" t="s">
+      <c r="A42" s="247"/>
+      <c r="B42" s="248"/>
+      <c r="C42" s="251" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="248"/>
-      <c r="E42" s="249"/>
-      <c r="F42" s="247" t="s">
+      <c r="D42" s="252"/>
+      <c r="E42" s="253"/>
+      <c r="F42" s="251" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="249"/>
+      <c r="G42" s="253"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="234"/>
-      <c r="F43" s="234"/>
-      <c r="G43" s="234"/>
+      <c r="E43" s="238"/>
+      <c r="F43" s="238"/>
+      <c r="G43" s="238"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -7009,21 +7012,21 @@
       <c r="B44" s="116"/>
       <c r="C44" s="118"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="235"/>
-      <c r="F44" s="235"/>
-      <c r="G44" s="235"/>
+      <c r="E44" s="239"/>
+      <c r="F44" s="239"/>
+      <c r="G44" s="239"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="283" t="s">
+      <c r="A46" s="287" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="283"/>
+      <c r="B46" s="287"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="283" t="s">
+      <c r="A47" s="287" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="283"/>
+      <c r="B47" s="287"/>
     </row>
   </sheetData>
   <mergeCells count="55">

--- a/backend/templates/UC-18gsm-250W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-250W-BFQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E870AAB6-61A0-4D02-B52E-3F81CFDE7565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64DA1A5-2435-45CE-AC13-51D52AC27F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -472,18 +472,6 @@
 T-0.00  U-4.00</t>
   </si>
   <si>
-    <t>Colour L
-L-55.00 T-60.00 U-65.00</t>
-  </si>
-  <si>
-    <t>Colour A
-L-45.00 T-50.00 U-55.00</t>
-  </si>
-  <si>
-    <t>Colour B
-L-(-16.00) T-(-11.00) U-(-6.00)</t>
-  </si>
-  <si>
     <t>Reference:</t>
   </si>
   <si>
@@ -517,6 +505,18 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Colour L
+L-57.50 T-61.50 U-65.50</t>
+  </si>
+  <si>
+    <t>Colour A
+L-46.00 T-51.00 U-56.00</t>
+  </si>
+  <si>
+    <t>Colour B
+L-(-14.00) T-(-11.00) U-(-8.00)</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="311">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1869,6 +1869,9 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2162,40 +2165,46 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2342,7 +2351,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2412,7 +2421,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="18">
     <dxf>
       <font>
         <strike/>
@@ -2453,44 +2462,6 @@
         <strike/>
         <color rgb="FFFF0000"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2611,45 +2582,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3059,35 +2991,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3108,12 +3040,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="144"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="146"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="147"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3125,19 +3057,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="138"/>
-      <c r="K4" s="139"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="140"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="148"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="150"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3149,64 +3081,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="140"/>
-      <c r="K5" s="141"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="142"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="156" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="157"/>
-      <c r="C6" s="158"/>
+      <c r="A6" s="157" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="158"/>
+      <c r="C6" s="159"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="133"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="135"/>
+        <v>139</v>
+      </c>
+      <c r="G6" s="134"/>
+      <c r="H6" s="155"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="135"/>
+      <c r="K6" s="136"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="159" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136" t="s">
+      <c r="A7" s="160" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="136" t="s">
+      <c r="E7" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="136" t="s">
+      <c r="F7" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="151" t="s">
+      <c r="G7" s="152" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="151" t="s">
+      <c r="H7" s="152" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="136" t="s">
+      <c r="I7" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="136"/>
-      <c r="K7" s="137"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="138"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="160"/>
-      <c r="B8" s="153"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153" t="s">
+      <c r="A8" s="161"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="153"/>
-      <c r="G8" s="152"/>
-      <c r="H8" s="152"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3608,11 +3540,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="167" t="s">
+      <c r="A39" s="168" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="168"/>
-      <c r="C39" s="169"/>
+      <c r="B39" s="169"/>
+      <c r="C39" s="170"/>
       <c r="D39" s="35" t="e">
         <f t="shared" ref="D39:K39" si="0">AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3647,11 +3579,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="164" t="s">
+      <c r="A40" s="165" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="165"/>
-      <c r="C40" s="166"/>
+      <c r="B40" s="166"/>
+      <c r="C40" s="167"/>
       <c r="D40" s="38">
         <f t="shared" ref="D40:K40" si="1">MIN(D9:D38)</f>
         <v>0</v>
@@ -3686,11 +3618,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="161" t="s">
+      <c r="A41" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="162"/>
-      <c r="C41" s="163"/>
+      <c r="B41" s="163"/>
+      <c r="C41" s="164"/>
       <c r="D41" s="41">
         <f t="shared" ref="D41:K41" si="2">MAX(D9:D38)</f>
         <v>0</v>
@@ -3731,8 +3663,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="170"/>
-      <c r="C42" s="170"/>
+      <c r="B42" s="171"/>
+      <c r="C42" s="171"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -3749,8 +3681,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="171"/>
-      <c r="C43" s="171"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -3759,15 +3691,15 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="155" t="s">
+      <c r="A44" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="155"/>
-      <c r="C44" s="155"/>
+      <c r="B44" s="156"/>
+      <c r="C44" s="156"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G44" s="46">
         <v>461309100</v>
@@ -3775,11 +3707,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="155" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" s="155"/>
-      <c r="C45" s="155"/>
+      <c r="A45" s="156" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" s="156"/>
+      <c r="C45" s="156"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -3849,64 +3781,48 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D9:D41">
-    <cfRule type="cellIs" dxfId="24" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="13" operator="notBetween">
+      <formula>17</formula>
       <formula>20</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="14" operator="lessThan">
-      <formula>17</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E41">
-    <cfRule type="cellIs" dxfId="22" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="11" operator="notBetween">
+      <formula>18</formula>
       <formula>28</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="lessThan">
-      <formula>18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F41">
-    <cfRule type="cellIs" dxfId="20" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="notBetween">
+      <formula>360</formula>
       <formula>400</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="10" operator="lessThan">
-      <formula>360</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G41">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="notBetween">
+      <formula>0.3</formula>
       <formula>0.6</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="lessThan">
-      <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H38">
-    <cfRule type="cellIs" dxfId="16" priority="1" stopIfTrue="1" operator="notBetween">
-      <formula>0.6</formula>
-      <formula>1.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="1" stopIfTrue="1" operator="notBetween">
       <formula>0.6</formula>
       <formula>1.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I41">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="notBetween">
+      <formula>900</formula>
       <formula>1200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="lessThan">
-      <formula>900</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J41">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="lessThan">
       <formula>350</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K41">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3929,35 +3845,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3978,18 +3894,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="144">
+      <c r="B4" s="145">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="176">
+      <c r="C4" s="177">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="177"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -4007,25 +3923,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="178">
+      <c r="J4" s="179">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="179"/>
+      <c r="K4" s="180"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="148">
+      <c r="B5" s="149">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="149">
+      <c r="C5" s="150">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="150"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -4043,104 +3959,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="194">
+      <c r="J5" s="195">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="195"/>
+      <c r="K5" s="196"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="212" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="213"/>
-      <c r="C6" s="214"/>
-      <c r="D6" s="196"/>
-      <c r="E6" s="197"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="185"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="211"/>
+      <c r="A6" s="213" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="214"/>
+      <c r="C6" s="215"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="186"/>
+      <c r="I6" s="211"/>
+      <c r="J6" s="212"/>
       <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="196" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="197"/>
-      <c r="C7" s="197"/>
-      <c r="D7" s="215" t="s">
+      <c r="A7" s="197" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="216" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="197"/>
-      <c r="F7" s="177"/>
-      <c r="G7" s="184" t="s">
+      <c r="E7" s="198"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="185" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="197"/>
-      <c r="I7" s="184" t="s">
-        <v>135</v>
-      </c>
-      <c r="J7" s="185"/>
-      <c r="K7" s="203" t="s">
+      <c r="H7" s="198"/>
+      <c r="I7" s="185" t="s">
+        <v>132</v>
+      </c>
+      <c r="J7" s="186"/>
+      <c r="K7" s="204" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
-      <c r="B8" s="199"/>
-      <c r="C8" s="199"/>
-      <c r="D8" s="198" t="s">
+      <c r="A8" s="199"/>
+      <c r="B8" s="200"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="207" t="s">
+      <c r="E8" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="208" t="s">
+      <c r="F8" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="200"/>
-      <c r="H8" s="199"/>
-      <c r="I8" s="200" t="s">
-        <v>136</v>
-      </c>
-      <c r="J8" s="208"/>
-      <c r="K8" s="204"/>
+      <c r="G8" s="201"/>
+      <c r="H8" s="200"/>
+      <c r="I8" s="201" t="s">
+        <v>133</v>
+      </c>
+      <c r="J8" s="209"/>
+      <c r="K8" s="205"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
-      <c r="B9" s="199"/>
-      <c r="C9" s="199"/>
-      <c r="D9" s="198"/>
-      <c r="E9" s="151"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="200"/>
-      <c r="H9" s="199"/>
+      <c r="A9" s="199"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="209"/>
+      <c r="G9" s="201"/>
+      <c r="H9" s="200"/>
       <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
       <c r="J9" s="58">
         <v>250</v>
       </c>
-      <c r="K9" s="204"/>
+      <c r="K9" s="205"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="198"/>
-      <c r="B10" s="199"/>
-      <c r="C10" s="199"/>
-      <c r="D10" s="206"/>
-      <c r="E10" s="152"/>
-      <c r="F10" s="209"/>
-      <c r="G10" s="201"/>
-      <c r="H10" s="202"/>
+      <c r="A10" s="199"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
+      <c r="D10" s="207"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="210"/>
+      <c r="G10" s="202"/>
+      <c r="H10" s="203"/>
       <c r="I10" s="59" t="s">
         <v>124</v>
       </c>
       <c r="J10" s="60">
         <v>253</v>
       </c>
-      <c r="K10" s="205"/>
+      <c r="K10" s="206"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="120">
@@ -4158,10 +4074,10 @@
       <c r="D11" s="61"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="193"/>
-      <c r="H11" s="193"/>
-      <c r="I11" s="180"/>
-      <c r="J11" s="181"/>
+      <c r="G11" s="194"/>
+      <c r="H11" s="194"/>
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
       <c r="K11" s="62"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4180,10 +4096,10 @@
       <c r="D12" s="63"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="192"/>
-      <c r="H12" s="192"/>
-      <c r="I12" s="182"/>
-      <c r="J12" s="183"/>
+      <c r="G12" s="193"/>
+      <c r="H12" s="193"/>
+      <c r="I12" s="183"/>
+      <c r="J12" s="184"/>
       <c r="K12" s="64"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4202,10 +4118,10 @@
       <c r="D13" s="63"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="192"/>
-      <c r="H13" s="192"/>
-      <c r="I13" s="182"/>
-      <c r="J13" s="183"/>
+      <c r="G13" s="193"/>
+      <c r="H13" s="193"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="184"/>
       <c r="K13" s="64"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4224,10 +4140,10 @@
       <c r="D14" s="63"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="192"/>
-      <c r="H14" s="192"/>
-      <c r="I14" s="182"/>
-      <c r="J14" s="183"/>
+      <c r="G14" s="193"/>
+      <c r="H14" s="193"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="184"/>
       <c r="K14" s="64"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4246,10 +4162,10 @@
       <c r="D15" s="63"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="192"/>
-      <c r="H15" s="192"/>
-      <c r="I15" s="182"/>
-      <c r="J15" s="183"/>
+      <c r="G15" s="193"/>
+      <c r="H15" s="193"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="184"/>
       <c r="K15" s="64"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4268,10 +4184,10 @@
       <c r="D16" s="61"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="193"/>
-      <c r="H16" s="193"/>
-      <c r="I16" s="182"/>
-      <c r="J16" s="183"/>
+      <c r="G16" s="194"/>
+      <c r="H16" s="194"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="184"/>
       <c r="K16" s="62"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4290,10 +4206,10 @@
       <c r="D17" s="63"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="192"/>
-      <c r="H17" s="192"/>
-      <c r="I17" s="182"/>
-      <c r="J17" s="183"/>
+      <c r="G17" s="193"/>
+      <c r="H17" s="193"/>
+      <c r="I17" s="183"/>
+      <c r="J17" s="184"/>
       <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4312,10 +4228,10 @@
       <c r="D18" s="63"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="192"/>
-      <c r="H18" s="192"/>
-      <c r="I18" s="182"/>
-      <c r="J18" s="183"/>
+      <c r="G18" s="193"/>
+      <c r="H18" s="193"/>
+      <c r="I18" s="183"/>
+      <c r="J18" s="184"/>
       <c r="K18" s="64"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4334,10 +4250,10 @@
       <c r="D19" s="63"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="192"/>
-      <c r="H19" s="192"/>
-      <c r="I19" s="182"/>
-      <c r="J19" s="183"/>
+      <c r="G19" s="193"/>
+      <c r="H19" s="193"/>
+      <c r="I19" s="183"/>
+      <c r="J19" s="184"/>
       <c r="K19" s="64"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4356,10 +4272,10 @@
       <c r="D20" s="63"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="188"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="182"/>
-      <c r="J20" s="183"/>
+      <c r="G20" s="189"/>
+      <c r="H20" s="190"/>
+      <c r="I20" s="183"/>
+      <c r="J20" s="184"/>
       <c r="K20" s="64"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4378,10 +4294,10 @@
       <c r="D21" s="63"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="188"/>
-      <c r="H21" s="189"/>
-      <c r="I21" s="182"/>
-      <c r="J21" s="183"/>
+      <c r="G21" s="189"/>
+      <c r="H21" s="190"/>
+      <c r="I21" s="183"/>
+      <c r="J21" s="184"/>
       <c r="K21" s="64"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4400,10 +4316,10 @@
       <c r="D22" s="63"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="188"/>
-      <c r="H22" s="189"/>
-      <c r="I22" s="182"/>
-      <c r="J22" s="183"/>
+      <c r="G22" s="189"/>
+      <c r="H22" s="190"/>
+      <c r="I22" s="183"/>
+      <c r="J22" s="184"/>
       <c r="K22" s="64"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4422,10 +4338,10 @@
       <c r="D23" s="63"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="188"/>
-      <c r="H23" s="189"/>
-      <c r="I23" s="182"/>
-      <c r="J23" s="183"/>
+      <c r="G23" s="189"/>
+      <c r="H23" s="190"/>
+      <c r="I23" s="183"/>
+      <c r="J23" s="184"/>
       <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4444,10 +4360,10 @@
       <c r="D24" s="63"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="188"/>
-      <c r="H24" s="189"/>
-      <c r="I24" s="182"/>
-      <c r="J24" s="183"/>
+      <c r="G24" s="189"/>
+      <c r="H24" s="190"/>
+      <c r="I24" s="183"/>
+      <c r="J24" s="184"/>
       <c r="K24" s="64"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4466,10 +4382,10 @@
       <c r="D25" s="63"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="188"/>
-      <c r="H25" s="189"/>
-      <c r="I25" s="182"/>
-      <c r="J25" s="183"/>
+      <c r="G25" s="189"/>
+      <c r="H25" s="190"/>
+      <c r="I25" s="183"/>
+      <c r="J25" s="184"/>
       <c r="K25" s="64"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4488,10 +4404,10 @@
       <c r="D26" s="63"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="188"/>
-      <c r="H26" s="189"/>
-      <c r="I26" s="182"/>
-      <c r="J26" s="183"/>
+      <c r="G26" s="189"/>
+      <c r="H26" s="190"/>
+      <c r="I26" s="183"/>
+      <c r="J26" s="184"/>
       <c r="K26" s="64"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4510,10 +4426,10 @@
       <c r="D27" s="63"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="188"/>
-      <c r="H27" s="189"/>
-      <c r="I27" s="182"/>
-      <c r="J27" s="183"/>
+      <c r="G27" s="189"/>
+      <c r="H27" s="190"/>
+      <c r="I27" s="183"/>
+      <c r="J27" s="184"/>
       <c r="K27" s="64"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4532,10 +4448,10 @@
       <c r="D28" s="63"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="188"/>
-      <c r="H28" s="189"/>
-      <c r="I28" s="182"/>
-      <c r="J28" s="183"/>
+      <c r="G28" s="189"/>
+      <c r="H28" s="190"/>
+      <c r="I28" s="183"/>
+      <c r="J28" s="184"/>
       <c r="K28" s="64"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4554,10 +4470,10 @@
       <c r="D29" s="63"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="188"/>
-      <c r="H29" s="189"/>
-      <c r="I29" s="182"/>
-      <c r="J29" s="183"/>
+      <c r="G29" s="189"/>
+      <c r="H29" s="190"/>
+      <c r="I29" s="183"/>
+      <c r="J29" s="184"/>
       <c r="K29" s="64"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4576,10 +4492,10 @@
       <c r="D30" s="63"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="188"/>
-      <c r="H30" s="189"/>
-      <c r="I30" s="182"/>
-      <c r="J30" s="183"/>
+      <c r="G30" s="189"/>
+      <c r="H30" s="190"/>
+      <c r="I30" s="183"/>
+      <c r="J30" s="184"/>
       <c r="K30" s="64"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4598,10 +4514,10 @@
       <c r="D31" s="63"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="188"/>
-      <c r="H31" s="189"/>
-      <c r="I31" s="182"/>
-      <c r="J31" s="183"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="190"/>
+      <c r="I31" s="183"/>
+      <c r="J31" s="184"/>
       <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4620,10 +4536,10 @@
       <c r="D32" s="63"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="188"/>
-      <c r="H32" s="189"/>
-      <c r="I32" s="182"/>
-      <c r="J32" s="183"/>
+      <c r="G32" s="189"/>
+      <c r="H32" s="190"/>
+      <c r="I32" s="183"/>
+      <c r="J32" s="184"/>
       <c r="K32" s="64"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4642,10 +4558,10 @@
       <c r="D33" s="63"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="188"/>
-      <c r="H33" s="189"/>
-      <c r="I33" s="182"/>
-      <c r="J33" s="183"/>
+      <c r="G33" s="189"/>
+      <c r="H33" s="190"/>
+      <c r="I33" s="183"/>
+      <c r="J33" s="184"/>
       <c r="K33" s="64"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4664,10 +4580,10 @@
       <c r="D34" s="63"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="188"/>
-      <c r="H34" s="189"/>
-      <c r="I34" s="182"/>
-      <c r="J34" s="183"/>
+      <c r="G34" s="189"/>
+      <c r="H34" s="190"/>
+      <c r="I34" s="183"/>
+      <c r="J34" s="184"/>
       <c r="K34" s="64"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4686,10 +4602,10 @@
       <c r="D35" s="63"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="188"/>
-      <c r="H35" s="189"/>
-      <c r="I35" s="182"/>
-      <c r="J35" s="183"/>
+      <c r="G35" s="189"/>
+      <c r="H35" s="190"/>
+      <c r="I35" s="183"/>
+      <c r="J35" s="184"/>
       <c r="K35" s="64"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4708,10 +4624,10 @@
       <c r="D36" s="63"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="188"/>
-      <c r="H36" s="189"/>
-      <c r="I36" s="182"/>
-      <c r="J36" s="183"/>
+      <c r="G36" s="189"/>
+      <c r="H36" s="190"/>
+      <c r="I36" s="183"/>
+      <c r="J36" s="184"/>
       <c r="K36" s="64"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4730,10 +4646,10 @@
       <c r="D37" s="63"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="188"/>
-      <c r="H37" s="189"/>
-      <c r="I37" s="182"/>
-      <c r="J37" s="183"/>
+      <c r="G37" s="189"/>
+      <c r="H37" s="190"/>
+      <c r="I37" s="183"/>
+      <c r="J37" s="184"/>
       <c r="K37" s="64"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4752,10 +4668,10 @@
       <c r="D38" s="63"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="188"/>
-      <c r="H38" s="189"/>
-      <c r="I38" s="182"/>
-      <c r="J38" s="183"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="183"/>
+      <c r="J38" s="184"/>
       <c r="K38" s="64"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4774,10 +4690,10 @@
       <c r="D39" s="63"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="188"/>
-      <c r="H39" s="189"/>
-      <c r="I39" s="182"/>
-      <c r="J39" s="183"/>
+      <c r="G39" s="189"/>
+      <c r="H39" s="190"/>
+      <c r="I39" s="183"/>
+      <c r="J39" s="184"/>
       <c r="K39" s="64"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4796,18 +4712,18 @@
       <c r="D40" s="63"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="192"/>
-      <c r="H40" s="192"/>
-      <c r="I40" s="182"/>
-      <c r="J40" s="183"/>
+      <c r="G40" s="193"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="183"/>
+      <c r="J40" s="184"/>
       <c r="K40" s="64"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="172" t="s">
+      <c r="A41" s="173" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="173"/>
-      <c r="C41" s="173"/>
+      <c r="B41" s="174"/>
+      <c r="C41" s="174"/>
       <c r="D41" s="65" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4820,27 +4736,27 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="190" t="e">
+      <c r="G41" s="191" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="191"/>
-      <c r="I41" s="224" t="e">
+      <c r="H41" s="192"/>
+      <c r="I41" s="225" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="225"/>
+      <c r="J41" s="226"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="174" t="s">
+      <c r="A42" s="175" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="175"/>
-      <c r="C42" s="175"/>
+      <c r="B42" s="176"/>
+      <c r="C42" s="176"/>
       <c r="D42" s="66">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4853,27 +4769,27 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="186">
+      <c r="G42" s="187">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="187"/>
-      <c r="I42" s="222">
+      <c r="H42" s="188"/>
+      <c r="I42" s="223">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="223"/>
+      <c r="J42" s="224"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="220" t="s">
+      <c r="A43" s="221" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="221"/>
-      <c r="C43" s="221"/>
+      <c r="B43" s="222"/>
+      <c r="C43" s="222"/>
       <c r="D43" s="67">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4886,16 +4802,16 @@
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="216">
+      <c r="G43" s="217">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="217"/>
-      <c r="I43" s="218">
+      <c r="H43" s="218"/>
+      <c r="I43" s="219">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="219"/>
+      <c r="J43" s="220"/>
       <c r="K43" s="69">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4905,8 +4821,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="170"/>
-      <c r="C44" s="170"/>
+      <c r="B44" s="171"/>
+      <c r="C44" s="171"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -4923,8 +4839,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="171"/>
-      <c r="C45" s="171"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -4933,15 +4849,15 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="155" t="s">
+      <c r="A46" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="155"/>
-      <c r="C46" s="155"/>
+      <c r="B46" s="156"/>
+      <c r="C46" s="156"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G46" s="46">
         <f>Page1!G44</f>
@@ -4950,11 +4866,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="155" t="s">
-        <v>133</v>
-      </c>
-      <c r="B47" s="155"/>
-      <c r="C47" s="155"/>
+      <c r="A47" s="156" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="156"/>
+      <c r="C47" s="156"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -5106,37 +5022,37 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="notBetween">
+      <formula>700</formula>
       <formula>1000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="lessThan">
-      <formula>700</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:E43">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F43">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H19 G20:G39 G40:H43">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
-      <formula>60</formula>
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="notBetween">
+      <formula>45</formula>
+      <formula>55</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThan">
-      <formula>50</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:J43">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notBetween">
+      <formula>250</formula>
+      <formula>253</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K43">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="notBetween">
+      <formula>410</formula>
       <formula>450</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
-      <formula>410</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5158,35 +5074,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5207,18 +5123,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="144">
+      <c r="B4" s="145">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="176">
+      <c r="C4" s="177">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="177"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5236,25 +5152,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="178">
+      <c r="J4" s="179">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="179"/>
+      <c r="K4" s="180"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="148">
+      <c r="B5" s="149">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="149">
+      <c r="C5" s="150">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="150"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5272,79 +5188,79 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="194">
+      <c r="J5" s="195">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="195"/>
+      <c r="K5" s="196"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="229" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="230"/>
-      <c r="C6" s="231"/>
-      <c r="D6" s="232"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="154"/>
+      <c r="A6" s="227" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="228"/>
+      <c r="C6" s="229"/>
+      <c r="D6" s="230"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="155"/>
       <c r="H6" s="71"/>
-      <c r="I6" s="196"/>
-      <c r="J6" s="197"/>
-      <c r="K6" s="203"/>
+      <c r="I6" s="197"/>
+      <c r="J6" s="198"/>
+      <c r="K6" s="204"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="196" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="197"/>
-      <c r="C7" s="197"/>
-      <c r="D7" s="215" t="s">
+      <c r="A7" s="197" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="216" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="233"/>
-      <c r="F7" s="233"/>
-      <c r="G7" s="177"/>
-      <c r="H7" s="226" t="s">
+      <c r="E7" s="231"/>
+      <c r="F7" s="231"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="204" t="s">
         <v>126</v>
       </c>
-      <c r="I7" s="198"/>
-      <c r="J7" s="199"/>
-      <c r="K7" s="204"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="200"/>
+      <c r="K7" s="205"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
-      <c r="B8" s="199"/>
-      <c r="C8" s="199"/>
-      <c r="D8" s="236" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="207" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="207" t="s">
-        <v>131</v>
-      </c>
-      <c r="G8" s="207" t="s">
+      <c r="A8" s="199"/>
+      <c r="B8" s="200"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="235" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="237" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="237" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="239" t="s">
         <v>128</v>
       </c>
-      <c r="H8" s="227"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="199"/>
-      <c r="K8" s="204"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="199"/>
+      <c r="J8" s="200"/>
+      <c r="K8" s="205"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="198"/>
-      <c r="B9" s="199"/>
-      <c r="C9" s="199"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
-      <c r="G9" s="152"/>
-      <c r="H9" s="228"/>
-      <c r="I9" s="198"/>
-      <c r="J9" s="199"/>
-      <c r="K9" s="204"/>
+      <c r="A9" s="199"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="236"/>
+      <c r="E9" s="238"/>
+      <c r="F9" s="238"/>
+      <c r="G9" s="240"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="199"/>
+      <c r="J9" s="200"/>
+      <c r="K9" s="205"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="120">
@@ -5364,9 +5280,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="73"/>
       <c r="H10" s="74"/>
-      <c r="I10" s="198"/>
-      <c r="J10" s="199"/>
-      <c r="K10" s="204"/>
+      <c r="I10" s="199"/>
+      <c r="J10" s="200"/>
+      <c r="K10" s="205"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="123">
@@ -5386,9 +5302,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="76"/>
       <c r="H11" s="77"/>
-      <c r="I11" s="198"/>
-      <c r="J11" s="199"/>
-      <c r="K11" s="204"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="200"/>
+      <c r="K11" s="205"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="123">
@@ -5408,9 +5324,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="76"/>
       <c r="H12" s="77"/>
-      <c r="I12" s="198"/>
-      <c r="J12" s="199"/>
-      <c r="K12" s="204"/>
+      <c r="I12" s="199"/>
+      <c r="J12" s="200"/>
+      <c r="K12" s="205"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="123">
@@ -5430,9 +5346,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="73"/>
       <c r="H13" s="77"/>
-      <c r="I13" s="198"/>
-      <c r="J13" s="199"/>
-      <c r="K13" s="204"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="205"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="123">
@@ -5452,9 +5368,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="76"/>
       <c r="H14" s="77"/>
-      <c r="I14" s="198"/>
-      <c r="J14" s="199"/>
-      <c r="K14" s="204"/>
+      <c r="I14" s="199"/>
+      <c r="J14" s="200"/>
+      <c r="K14" s="205"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="123">
@@ -5474,9 +5390,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="76"/>
       <c r="H15" s="77"/>
-      <c r="I15" s="198"/>
-      <c r="J15" s="199"/>
-      <c r="K15" s="204"/>
+      <c r="I15" s="199"/>
+      <c r="J15" s="200"/>
+      <c r="K15" s="205"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="123">
@@ -5496,9 +5412,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="76"/>
       <c r="H16" s="77"/>
-      <c r="I16" s="198"/>
-      <c r="J16" s="199"/>
-      <c r="K16" s="204"/>
+      <c r="I16" s="199"/>
+      <c r="J16" s="200"/>
+      <c r="K16" s="205"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="123">
@@ -5518,9 +5434,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="76"/>
       <c r="H17" s="77"/>
-      <c r="I17" s="198"/>
-      <c r="J17" s="199"/>
-      <c r="K17" s="204"/>
+      <c r="I17" s="199"/>
+      <c r="J17" s="200"/>
+      <c r="K17" s="205"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="123">
@@ -5540,9 +5456,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="76"/>
       <c r="H18" s="77"/>
-      <c r="I18" s="198"/>
-      <c r="J18" s="199"/>
-      <c r="K18" s="204"/>
+      <c r="I18" s="199"/>
+      <c r="J18" s="200"/>
+      <c r="K18" s="205"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="123">
@@ -5562,9 +5478,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="76"/>
       <c r="H19" s="77"/>
-      <c r="I19" s="198"/>
-      <c r="J19" s="199"/>
-      <c r="K19" s="204"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="200"/>
+      <c r="K19" s="205"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
@@ -5584,9 +5500,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="76"/>
       <c r="H20" s="77"/>
-      <c r="I20" s="198"/>
-      <c r="J20" s="199"/>
-      <c r="K20" s="204"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="205"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="123">
@@ -5606,9 +5522,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="76"/>
       <c r="H21" s="77"/>
-      <c r="I21" s="198"/>
-      <c r="J21" s="199"/>
-      <c r="K21" s="204"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="200"/>
+      <c r="K21" s="205"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="123">
@@ -5628,9 +5544,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="76"/>
       <c r="H22" s="77"/>
-      <c r="I22" s="198"/>
-      <c r="J22" s="199"/>
-      <c r="K22" s="204"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="200"/>
+      <c r="K22" s="205"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="123">
@@ -5650,9 +5566,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="76"/>
       <c r="H23" s="77"/>
-      <c r="I23" s="198"/>
-      <c r="J23" s="199"/>
-      <c r="K23" s="204"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="205"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="123">
@@ -5672,9 +5588,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="76"/>
       <c r="H24" s="77"/>
-      <c r="I24" s="198"/>
-      <c r="J24" s="199"/>
-      <c r="K24" s="204"/>
+      <c r="I24" s="199"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="205"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="123">
@@ -5694,9 +5610,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="76"/>
       <c r="H25" s="77"/>
-      <c r="I25" s="198"/>
-      <c r="J25" s="199"/>
-      <c r="K25" s="204"/>
+      <c r="I25" s="199"/>
+      <c r="J25" s="200"/>
+      <c r="K25" s="205"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="123">
@@ -5716,9 +5632,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="76"/>
       <c r="H26" s="77"/>
-      <c r="I26" s="198"/>
-      <c r="J26" s="199"/>
-      <c r="K26" s="204"/>
+      <c r="I26" s="199"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="205"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="123">
@@ -5738,9 +5654,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="76"/>
       <c r="H27" s="77"/>
-      <c r="I27" s="198"/>
-      <c r="J27" s="199"/>
-      <c r="K27" s="204"/>
+      <c r="I27" s="199"/>
+      <c r="J27" s="200"/>
+      <c r="K27" s="205"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="123">
@@ -5760,9 +5676,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="76"/>
       <c r="H28" s="77"/>
-      <c r="I28" s="198"/>
-      <c r="J28" s="199"/>
-      <c r="K28" s="204"/>
+      <c r="I28" s="199"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="205"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="123">
@@ -5782,9 +5698,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="76"/>
       <c r="H29" s="77"/>
-      <c r="I29" s="198"/>
-      <c r="J29" s="199"/>
-      <c r="K29" s="204"/>
+      <c r="I29" s="199"/>
+      <c r="J29" s="200"/>
+      <c r="K29" s="205"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
@@ -5804,9 +5720,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="76"/>
       <c r="H30" s="77"/>
-      <c r="I30" s="198"/>
-      <c r="J30" s="199"/>
-      <c r="K30" s="204"/>
+      <c r="I30" s="199"/>
+      <c r="J30" s="200"/>
+      <c r="K30" s="205"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="123">
@@ -5826,9 +5742,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="76"/>
       <c r="H31" s="77"/>
-      <c r="I31" s="198"/>
-      <c r="J31" s="199"/>
-      <c r="K31" s="204"/>
+      <c r="I31" s="199"/>
+      <c r="J31" s="200"/>
+      <c r="K31" s="205"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="123">
@@ -5848,9 +5764,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="76"/>
       <c r="H32" s="77"/>
-      <c r="I32" s="198"/>
-      <c r="J32" s="199"/>
-      <c r="K32" s="204"/>
+      <c r="I32" s="199"/>
+      <c r="J32" s="200"/>
+      <c r="K32" s="205"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="123">
@@ -5870,9 +5786,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="76"/>
       <c r="H33" s="77"/>
-      <c r="I33" s="198"/>
-      <c r="J33" s="199"/>
-      <c r="K33" s="204"/>
+      <c r="I33" s="199"/>
+      <c r="J33" s="200"/>
+      <c r="K33" s="205"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="123">
@@ -5892,9 +5808,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="76"/>
       <c r="H34" s="77"/>
-      <c r="I34" s="198"/>
-      <c r="J34" s="199"/>
-      <c r="K34" s="204"/>
+      <c r="I34" s="199"/>
+      <c r="J34" s="200"/>
+      <c r="K34" s="205"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="123">
@@ -5914,9 +5830,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="76"/>
       <c r="H35" s="77"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="199"/>
-      <c r="K35" s="204"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="200"/>
+      <c r="K35" s="205"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="123">
@@ -5936,9 +5852,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="76"/>
       <c r="H36" s="77"/>
-      <c r="I36" s="198"/>
-      <c r="J36" s="199"/>
-      <c r="K36" s="204"/>
+      <c r="I36" s="199"/>
+      <c r="J36" s="200"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="123">
@@ -5958,9 +5874,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="76"/>
       <c r="H37" s="77"/>
-      <c r="I37" s="198"/>
-      <c r="J37" s="199"/>
-      <c r="K37" s="204"/>
+      <c r="I37" s="199"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="205"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="123">
@@ -5980,9 +5896,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="76"/>
       <c r="H38" s="77"/>
-      <c r="I38" s="198"/>
-      <c r="J38" s="199"/>
-      <c r="K38" s="204"/>
+      <c r="I38" s="199"/>
+      <c r="J38" s="200"/>
+      <c r="K38" s="205"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="130">
@@ -6002,16 +5918,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="76"/>
       <c r="H39" s="77"/>
-      <c r="I39" s="198"/>
-      <c r="J39" s="199"/>
-      <c r="K39" s="204"/>
+      <c r="I39" s="199"/>
+      <c r="J39" s="200"/>
+      <c r="K39" s="205"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="234" t="s">
+      <c r="A40" s="233" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="235"/>
-      <c r="C40" s="235"/>
+      <c r="B40" s="234"/>
+      <c r="C40" s="234"/>
       <c r="D40" s="78" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -6032,16 +5948,16 @@
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="199"/>
-      <c r="J40" s="199"/>
-      <c r="K40" s="204"/>
+      <c r="I40" s="200"/>
+      <c r="J40" s="200"/>
+      <c r="K40" s="205"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="174" t="s">
+      <c r="A41" s="175" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="175"/>
-      <c r="C41" s="175"/>
+      <c r="B41" s="176"/>
+      <c r="C41" s="176"/>
       <c r="D41" s="80">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -6062,16 +5978,16 @@
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="199"/>
-      <c r="J41" s="199"/>
-      <c r="K41" s="204"/>
+      <c r="I41" s="200"/>
+      <c r="J41" s="200"/>
+      <c r="K41" s="205"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="220" t="s">
+      <c r="A42" s="221" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="221"/>
-      <c r="C42" s="221"/>
+      <c r="B42" s="222"/>
+      <c r="C42" s="222"/>
       <c r="D42" s="82">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -6092,16 +6008,16 @@
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="202"/>
-      <c r="J42" s="202"/>
-      <c r="K42" s="205"/>
+      <c r="I42" s="203"/>
+      <c r="J42" s="203"/>
+      <c r="K42" s="206"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="170"/>
-      <c r="C43" s="170"/>
+      <c r="B43" s="171"/>
+      <c r="C43" s="171"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -6118,8 +6034,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="171"/>
-      <c r="C44" s="171"/>
+      <c r="B44" s="172"/>
+      <c r="C44" s="172"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -6128,15 +6044,15 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="155" t="s">
+      <c r="A45" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="155"/>
-      <c r="C45" s="155"/>
+      <c r="B45" s="156"/>
+      <c r="C45" s="156"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G45" s="46">
         <f>Page1!G44</f>
@@ -6145,11 +6061,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="155" t="s">
-        <v>133</v>
-      </c>
-      <c r="B46" s="155"/>
-      <c r="C46" s="155"/>
+      <c r="A46" s="156" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" s="156"/>
+      <c r="C46" s="156"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -6202,20 +6118,20 @@
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
-      <formula>52</formula>
-      <formula>64</formula>
+      <formula>57.5</formula>
+      <formula>65.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E42">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="notBetween">
-      <formula>49</formula>
-      <formula>59</formula>
+      <formula>46</formula>
+      <formula>56</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F42">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="notBetween">
-      <formula>-12.5</formula>
-      <formula>-4.5</formula>
+      <formula>-14</formula>
+      <formula>-8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:H42">
@@ -6224,6 +6140,12 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8:F9" xr:uid="{119C1EAE-9453-45F6-B9BC-276001B555A7}">
+      <formula1>1000</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -6245,15 +6167,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="288" t="s">
+      <c r="A1" s="291" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="289"/>
-      <c r="C1" s="289"/>
-      <c r="D1" s="289"/>
-      <c r="E1" s="289"/>
-      <c r="F1" s="289"/>
-      <c r="G1" s="290"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
+      <c r="G1" s="293"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -6267,37 +6189,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="296" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="297"/>
-      <c r="C3" s="297"/>
-      <c r="D3" s="297"/>
-      <c r="E3" s="297"/>
-      <c r="F3" s="297"/>
-      <c r="G3" s="298"/>
+      <c r="A3" s="299" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="300"/>
+      <c r="C3" s="300"/>
+      <c r="D3" s="300"/>
+      <c r="E3" s="300"/>
+      <c r="F3" s="300"/>
+      <c r="G3" s="301"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="198" t="s">
+      <c r="A4" s="199" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="199"/>
-      <c r="C4" s="199"/>
-      <c r="D4" s="199"/>
-      <c r="E4" s="199"/>
-      <c r="F4" s="199"/>
-      <c r="G4" s="204"/>
+      <c r="B4" s="200"/>
+      <c r="C4" s="200"/>
+      <c r="D4" s="200"/>
+      <c r="E4" s="200"/>
+      <c r="F4" s="200"/>
+      <c r="G4" s="205"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="291" t="s">
+      <c r="A5" s="294" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="292"/>
-      <c r="C5" s="292"/>
-      <c r="D5" s="292"/>
-      <c r="E5" s="292"/>
-      <c r="F5" s="292"/>
-      <c r="G5" s="293"/>
+      <c r="B5" s="295"/>
+      <c r="C5" s="295"/>
+      <c r="D5" s="295"/>
+      <c r="E5" s="295"/>
+      <c r="F5" s="295"/>
+      <c r="G5" s="296"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -6309,14 +6231,14 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="256" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" s="258"/>
-      <c r="F6" s="294" t="s">
+      <c r="D6" s="259" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="261"/>
+      <c r="F6" s="297" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="279">
+      <c r="G6" s="282">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6329,13 +6251,13 @@
       <c r="C7" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="256">
+      <c r="D7" s="259">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="258"/>
-      <c r="F7" s="294"/>
-      <c r="G7" s="295"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="297"/>
+      <c r="G7" s="298"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -6348,15 +6270,15 @@
       <c r="C8" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="297">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="294"/>
-      <c r="F8" s="276" t="s">
+      <c r="E8" s="297"/>
+      <c r="F8" s="279" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="279">
+      <c r="G8" s="282">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6369,15 +6291,15 @@
         <f>Page1!G44</f>
         <v>461309100</v>
       </c>
-      <c r="C9" s="276" t="s">
+      <c r="C9" s="279" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="282" t="s">
+      <c r="D9" s="285" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="283"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="280"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="280"/>
+      <c r="G9" s="283"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -6387,34 +6309,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="278"/>
-      <c r="D10" s="284"/>
-      <c r="E10" s="285"/>
-      <c r="F10" s="278"/>
-      <c r="G10" s="281"/>
+      <c r="C10" s="281"/>
+      <c r="D10" s="287"/>
+      <c r="E10" s="288"/>
+      <c r="F10" s="281"/>
+      <c r="G10" s="284"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="299" t="s">
+      <c r="A11" s="302" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="301" t="s">
+      <c r="B11" s="304" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="303" t="s">
+      <c r="C11" s="306" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="304"/>
-      <c r="E11" s="305"/>
-      <c r="F11" s="301" t="s">
+      <c r="D11" s="307"/>
+      <c r="E11" s="308"/>
+      <c r="F11" s="304" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="306" t="s">
+      <c r="G11" s="309" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="300"/>
-      <c r="B12" s="302"/>
+      <c r="A12" s="303"/>
+      <c r="B12" s="305"/>
       <c r="C12" s="99" t="s">
         <v>60</v>
       </c>
@@ -6424,8 +6346,8 @@
       <c r="E12" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="302"/>
-      <c r="G12" s="307"/>
+      <c r="F12" s="305"/>
+      <c r="G12" s="310"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -6495,7 +6417,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="286" t="s">
+      <c r="G15" s="239" t="s">
         <v>71</v>
       </c>
     </row>
@@ -6519,7 +6441,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="227"/>
+      <c r="G16" s="289"/>
     </row>
     <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
@@ -6541,7 +6463,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="227"/>
+      <c r="G17" s="289"/>
     </row>
     <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104" t="s">
@@ -6563,7 +6485,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="227"/>
+      <c r="G18" s="289"/>
     </row>
     <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104" t="s">
@@ -6585,7 +6507,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="227"/>
+      <c r="G19" s="289"/>
     </row>
     <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
@@ -6607,7 +6529,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="227"/>
+      <c r="G20" s="289"/>
     </row>
     <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
@@ -6629,7 +6551,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="227"/>
+      <c r="G21" s="289"/>
     </row>
     <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="104" t="s">
@@ -6651,7 +6573,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="137"/>
+      <c r="G22" s="138"/>
     </row>
     <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -6688,8 +6610,8 @@
         <v>39</v>
       </c>
       <c r="D24" s="39">
-        <f>Page2!J8</f>
-        <v>0</v>
+        <f>Page2!J9</f>
+        <v>250</v>
       </c>
       <c r="E24" s="39">
         <f>Page2!J10</f>
@@ -6751,26 +6673,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="270" t="s">
+      <c r="A27" s="273" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="271"/>
-      <c r="C27" s="271"/>
-      <c r="D27" s="271"/>
-      <c r="E27" s="271"/>
-      <c r="F27" s="271"/>
-      <c r="G27" s="272"/>
+      <c r="B27" s="274"/>
+      <c r="C27" s="274"/>
+      <c r="D27" s="274"/>
+      <c r="E27" s="274"/>
+      <c r="F27" s="274"/>
+      <c r="G27" s="275"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="254" t="s">
+      <c r="A28" s="257" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="255"/>
-      <c r="C28" s="273" t="s">
+      <c r="B28" s="258"/>
+      <c r="C28" s="276" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="274"/>
-      <c r="E28" s="275"/>
+      <c r="D28" s="277"/>
+      <c r="E28" s="278"/>
       <c r="F28" s="113" t="s">
         <v>92</v>
       </c>
@@ -6779,15 +6701,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="259" t="s">
+      <c r="A29" s="262" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="258"/>
-      <c r="C29" s="264" t="s">
+      <c r="B29" s="261"/>
+      <c r="C29" s="267" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="265"/>
-      <c r="E29" s="266"/>
+      <c r="D29" s="268"/>
+      <c r="E29" s="269"/>
       <c r="F29" s="66" t="s">
         <v>92</v>
       </c>
@@ -6796,15 +6718,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="259" t="s">
+      <c r="A30" s="262" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="258"/>
-      <c r="C30" s="264" t="s">
+      <c r="B30" s="261"/>
+      <c r="C30" s="267" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="265"/>
-      <c r="E30" s="266"/>
+      <c r="D30" s="268"/>
+      <c r="E30" s="269"/>
       <c r="F30" s="66" t="s">
         <v>92</v>
       </c>
@@ -6813,15 +6735,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="259" t="s">
+      <c r="A31" s="262" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="258"/>
-      <c r="C31" s="264" t="s">
+      <c r="B31" s="261"/>
+      <c r="C31" s="267" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="265"/>
-      <c r="E31" s="266"/>
+      <c r="D31" s="268"/>
+      <c r="E31" s="269"/>
       <c r="F31" s="66" t="s">
         <v>92</v>
       </c>
@@ -6830,15 +6752,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="259" t="s">
+      <c r="A32" s="262" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="258"/>
-      <c r="C32" s="264" t="s">
+      <c r="B32" s="261"/>
+      <c r="C32" s="267" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="265"/>
-      <c r="E32" s="266"/>
+      <c r="D32" s="268"/>
+      <c r="E32" s="269"/>
       <c r="F32" s="66" t="s">
         <v>92</v>
       </c>
@@ -6846,61 +6768,61 @@
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="259" t="s">
+    <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="262" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="258"/>
-      <c r="C33" s="264" t="s">
+      <c r="B33" s="261"/>
+      <c r="C33" s="267" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="265"/>
-      <c r="E33" s="266"/>
+      <c r="D33" s="268"/>
+      <c r="E33" s="269"/>
       <c r="F33" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="G33" s="108" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="147" t="s">
+      <c r="A34" s="148" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="148"/>
-      <c r="C34" s="267" t="s">
+      <c r="B34" s="149"/>
+      <c r="C34" s="270" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="268"/>
-      <c r="E34" s="269"/>
+      <c r="D34" s="271"/>
+      <c r="E34" s="272"/>
       <c r="F34" s="114" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="133" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="270" t="s">
+      <c r="A35" s="273" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="271"/>
-      <c r="C35" s="271"/>
-      <c r="D35" s="271"/>
-      <c r="E35" s="271"/>
-      <c r="F35" s="271"/>
-      <c r="G35" s="272"/>
+      <c r="B35" s="274"/>
+      <c r="C35" s="274"/>
+      <c r="D35" s="274"/>
+      <c r="E35" s="274"/>
+      <c r="F35" s="274"/>
+      <c r="G35" s="275"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="143" t="s">
+      <c r="A36" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="144"/>
-      <c r="C36" s="262" t="s">
+      <c r="B36" s="145"/>
+      <c r="C36" s="265" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="263"/>
-      <c r="E36" s="144"/>
+      <c r="D36" s="266"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="10" t="s">
         <v>92</v>
       </c>
@@ -6909,15 +6831,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="254" t="s">
+      <c r="A37" s="257" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="255"/>
-      <c r="C37" s="256" t="s">
+      <c r="B37" s="258"/>
+      <c r="C37" s="259" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="257"/>
-      <c r="E37" s="258"/>
+      <c r="D37" s="260"/>
+      <c r="E37" s="261"/>
       <c r="F37" s="106" t="s">
         <v>92</v>
       </c>
@@ -6926,15 +6848,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="259" t="s">
+      <c r="A38" s="262" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="258"/>
-      <c r="C38" s="256" t="s">
+      <c r="B38" s="261"/>
+      <c r="C38" s="259" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="257"/>
-      <c r="E38" s="258"/>
+      <c r="D38" s="260"/>
+      <c r="E38" s="261"/>
       <c r="F38" s="106" t="s">
         <v>92</v>
       </c>
@@ -6943,15 +6865,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="147" t="s">
+      <c r="A39" s="148" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="148"/>
-      <c r="C39" s="260" t="s">
+      <c r="B39" s="149"/>
+      <c r="C39" s="263" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="261"/>
-      <c r="E39" s="148"/>
+      <c r="D39" s="264"/>
+      <c r="E39" s="149"/>
       <c r="F39" s="1" t="s">
         <v>92</v>
       </c>
@@ -6960,50 +6882,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="243" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="241"/>
-      <c r="C40" s="242" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="243"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="242" t="s">
-        <v>138</v>
-      </c>
-      <c r="G40" s="244"/>
+      <c r="B40" s="244"/>
+      <c r="C40" s="245" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="246"/>
+      <c r="E40" s="247"/>
+      <c r="F40" s="245" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40" s="247"/>
     </row>
     <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="245"/>
-      <c r="B41" s="246"/>
-      <c r="C41" s="198"/>
-      <c r="D41" s="199"/>
-      <c r="E41" s="204"/>
-      <c r="F41" s="249"/>
-      <c r="G41" s="250"/>
+      <c r="A41" s="248"/>
+      <c r="B41" s="249"/>
+      <c r="C41" s="199"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="205"/>
+      <c r="F41" s="252"/>
+      <c r="G41" s="253"/>
     </row>
     <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="247"/>
-      <c r="B42" s="248"/>
-      <c r="C42" s="251" t="s">
+      <c r="A42" s="250"/>
+      <c r="B42" s="251"/>
+      <c r="C42" s="254" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="252"/>
-      <c r="E42" s="253"/>
-      <c r="F42" s="251" t="s">
-        <v>139</v>
-      </c>
-      <c r="G42" s="253"/>
+      <c r="D42" s="255"/>
+      <c r="E42" s="256"/>
+      <c r="F42" s="254" t="s">
+        <v>136</v>
+      </c>
+      <c r="G42" s="256"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="238"/>
-      <c r="F43" s="238"/>
-      <c r="G43" s="238"/>
+      <c r="E43" s="241"/>
+      <c r="F43" s="241"/>
+      <c r="G43" s="241"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -7012,21 +6934,21 @@
       <c r="B44" s="116"/>
       <c r="C44" s="118"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="239"/>
-      <c r="F44" s="239"/>
-      <c r="G44" s="239"/>
+      <c r="E44" s="242"/>
+      <c r="F44" s="242"/>
+      <c r="G44" s="242"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="287" t="s">
+      <c r="A46" s="290" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="287"/>
+      <c r="B46" s="290"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="287" t="s">
+      <c r="A47" s="290" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="287"/>
+      <c r="B47" s="290"/>
     </row>
   </sheetData>
   <mergeCells count="55">

--- a/backend/templates/UC-18gsm-250W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-250W-BFQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64DA1A5-2435-45CE-AC13-51D52AC27F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8013345-787B-4F42-ADEC-3FA841D92683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="142">
   <si>
     <t>Sample No.</t>
   </si>
@@ -499,9 +499,6 @@
   </si>
   <si>
     <t>Swanson Plastics(India) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>#02</t>
   </si>
   <si>
     <t>NA</t>
@@ -1872,6 +1869,63 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1881,9 +1935,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1938,153 +1989,66 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2123,6 +2087,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2135,77 +2102,269 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2254,168 +2413,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2991,35 +2988,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3040,12 +3037,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="147"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="165"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3057,19 +3054,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="139"/>
-      <c r="K4" s="140"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="158"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149"/>
-      <c r="C5" s="150"/>
-      <c r="D5" s="151"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3081,64 +3078,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="141"/>
-      <c r="K5" s="142"/>
+      <c r="J5" s="159"/>
+      <c r="K5" s="160"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="135" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="158"/>
-      <c r="C6" s="159"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="137"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G6" s="134"/>
-      <c r="H6" s="155"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="136"/>
+        <v>138</v>
+      </c>
+      <c r="G6" s="153"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="154"/>
+      <c r="K6" s="155"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="160" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137" t="s">
+      <c r="A7" s="138" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="137" t="s">
+      <c r="F7" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="152" t="s">
+      <c r="G7" s="170" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="152" t="s">
+      <c r="H7" s="170" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="137" t="s">
+      <c r="I7" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="137"/>
-      <c r="K7" s="138"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="156"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="161"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="154"/>
-      <c r="D8" s="154"/>
-      <c r="E8" s="154" t="s">
+      <c r="A8" s="140"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="154"/>
-      <c r="G8" s="153"/>
-      <c r="H8" s="153"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="171"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3540,11 +3537,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="168" t="s">
+      <c r="A39" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="169"/>
-      <c r="C39" s="170"/>
+      <c r="B39" s="149"/>
+      <c r="C39" s="150"/>
       <c r="D39" s="35" t="e">
         <f t="shared" ref="D39:K39" si="0">AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3579,11 +3576,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="165" t="s">
+      <c r="A40" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="166"/>
-      <c r="C40" s="167"/>
+      <c r="B40" s="146"/>
+      <c r="C40" s="147"/>
       <c r="D40" s="38">
         <f t="shared" ref="D40:K40" si="1">MIN(D9:D38)</f>
         <v>0</v>
@@ -3618,11 +3615,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="162" t="s">
+      <c r="A41" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="163"/>
-      <c r="C41" s="164"/>
+      <c r="B41" s="143"/>
+      <c r="C41" s="144"/>
       <c r="D41" s="41">
         <f t="shared" ref="D41:K41" si="2">MAX(D9:D38)</f>
         <v>0</v>
@@ -3663,8 +3660,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="171"/>
-      <c r="C42" s="171"/>
+      <c r="B42" s="151"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -3681,8 +3678,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -3691,11 +3688,11 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="156" t="s">
+      <c r="A44" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="156"/>
-      <c r="C44" s="156"/>
+      <c r="B44" s="134"/>
+      <c r="C44" s="134"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
@@ -3707,11 +3704,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="156" t="s">
+      <c r="A45" s="134" t="s">
         <v>130</v>
       </c>
-      <c r="B45" s="156"/>
-      <c r="C45" s="156"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="134"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -3753,15 +3750,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="25">
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="B43:C43"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
@@ -3778,6 +3766,15 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D9:D41">
@@ -3845,35 +3842,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3894,18 +3891,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145">
+      <c r="B4" s="163">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="177">
+      <c r="C4" s="220">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="178"/>
+      <c r="D4" s="209"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3923,25 +3920,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="179">
+      <c r="J4" s="221">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="180"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149">
+      <c r="B5" s="167">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="150">
+      <c r="C5" s="168">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="151"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3959,104 +3956,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="195">
+      <c r="J5" s="185">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="196"/>
+      <c r="K5" s="186"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="213" t="s">
+      <c r="A6" s="205" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="214"/>
-      <c r="C6" s="215"/>
-      <c r="D6" s="197"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="185"/>
-      <c r="H6" s="186"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="212"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="207"/>
+      <c r="D6" s="187"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="204"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="204"/>
+      <c r="I6" s="202"/>
+      <c r="J6" s="203"/>
       <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="216" t="s">
+      <c r="A7" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="198"/>
-      <c r="F7" s="178"/>
-      <c r="G7" s="185" t="s">
+      <c r="E7" s="188"/>
+      <c r="F7" s="209"/>
+      <c r="G7" s="191" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="198"/>
-      <c r="I7" s="185" t="s">
+      <c r="H7" s="188"/>
+      <c r="I7" s="191" t="s">
         <v>132</v>
       </c>
-      <c r="J7" s="186"/>
-      <c r="K7" s="204" t="s">
+      <c r="J7" s="204"/>
+      <c r="K7" s="195" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="199"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="200"/>
-      <c r="D8" s="199" t="s">
+      <c r="A8" s="189"/>
+      <c r="B8" s="190"/>
+      <c r="C8" s="190"/>
+      <c r="D8" s="189" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="208" t="s">
+      <c r="E8" s="199" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="209" t="s">
+      <c r="F8" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="201"/>
-      <c r="H8" s="200"/>
-      <c r="I8" s="201" t="s">
+      <c r="G8" s="192"/>
+      <c r="H8" s="190"/>
+      <c r="I8" s="192" t="s">
         <v>133</v>
       </c>
-      <c r="J8" s="209"/>
-      <c r="K8" s="205"/>
+      <c r="J8" s="200"/>
+      <c r="K8" s="196"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="199"/>
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="199"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="201"/>
-      <c r="H9" s="200"/>
+      <c r="A9" s="189"/>
+      <c r="B9" s="190"/>
+      <c r="C9" s="190"/>
+      <c r="D9" s="189"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="200"/>
+      <c r="G9" s="192"/>
+      <c r="H9" s="190"/>
       <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
       <c r="J9" s="58">
         <v>250</v>
       </c>
-      <c r="K9" s="205"/>
+      <c r="K9" s="196"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="199"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
-      <c r="D10" s="207"/>
-      <c r="E10" s="153"/>
-      <c r="F10" s="210"/>
-      <c r="G10" s="202"/>
-      <c r="H10" s="203"/>
+      <c r="A10" s="189"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="190"/>
+      <c r="D10" s="198"/>
+      <c r="E10" s="171"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="193"/>
+      <c r="H10" s="194"/>
       <c r="I10" s="59" t="s">
         <v>124</v>
       </c>
       <c r="J10" s="60">
         <v>253</v>
       </c>
-      <c r="K10" s="206"/>
+      <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="120">
@@ -4074,10 +4071,10 @@
       <c r="D11" s="61"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="194"/>
-      <c r="H11" s="194"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="182"/>
+      <c r="G11" s="212"/>
+      <c r="H11" s="212"/>
+      <c r="I11" s="223"/>
+      <c r="J11" s="224"/>
       <c r="K11" s="62"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4096,10 +4093,10 @@
       <c r="D12" s="63"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="193"/>
-      <c r="H12" s="193"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="184"/>
+      <c r="G12" s="213"/>
+      <c r="H12" s="213"/>
+      <c r="I12" s="175"/>
+      <c r="J12" s="176"/>
       <c r="K12" s="64"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4118,10 +4115,10 @@
       <c r="D13" s="63"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="193"/>
-      <c r="H13" s="193"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="184"/>
+      <c r="G13" s="213"/>
+      <c r="H13" s="213"/>
+      <c r="I13" s="175"/>
+      <c r="J13" s="176"/>
       <c r="K13" s="64"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4140,10 +4137,10 @@
       <c r="D14" s="63"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="193"/>
-      <c r="H14" s="193"/>
-      <c r="I14" s="183"/>
-      <c r="J14" s="184"/>
+      <c r="G14" s="213"/>
+      <c r="H14" s="213"/>
+      <c r="I14" s="175"/>
+      <c r="J14" s="176"/>
       <c r="K14" s="64"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4162,10 +4159,10 @@
       <c r="D15" s="63"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="193"/>
-      <c r="H15" s="193"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="184"/>
+      <c r="G15" s="213"/>
+      <c r="H15" s="213"/>
+      <c r="I15" s="175"/>
+      <c r="J15" s="176"/>
       <c r="K15" s="64"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4184,10 +4181,10 @@
       <c r="D16" s="61"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="194"/>
-      <c r="H16" s="194"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="184"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="I16" s="175"/>
+      <c r="J16" s="176"/>
       <c r="K16" s="62"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4206,10 +4203,10 @@
       <c r="D17" s="63"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="193"/>
-      <c r="H17" s="193"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="184"/>
+      <c r="G17" s="213"/>
+      <c r="H17" s="213"/>
+      <c r="I17" s="175"/>
+      <c r="J17" s="176"/>
       <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4228,10 +4225,10 @@
       <c r="D18" s="63"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="193"/>
-      <c r="H18" s="193"/>
-      <c r="I18" s="183"/>
-      <c r="J18" s="184"/>
+      <c r="G18" s="213"/>
+      <c r="H18" s="213"/>
+      <c r="I18" s="175"/>
+      <c r="J18" s="176"/>
       <c r="K18" s="64"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4250,10 +4247,10 @@
       <c r="D19" s="63"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="193"/>
-      <c r="H19" s="193"/>
-      <c r="I19" s="183"/>
-      <c r="J19" s="184"/>
+      <c r="G19" s="213"/>
+      <c r="H19" s="213"/>
+      <c r="I19" s="175"/>
+      <c r="J19" s="176"/>
       <c r="K19" s="64"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4272,10 +4269,10 @@
       <c r="D20" s="63"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="183"/>
-      <c r="J20" s="184"/>
+      <c r="G20" s="210"/>
+      <c r="H20" s="211"/>
+      <c r="I20" s="175"/>
+      <c r="J20" s="176"/>
       <c r="K20" s="64"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4294,10 +4291,10 @@
       <c r="D21" s="63"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="189"/>
-      <c r="H21" s="190"/>
-      <c r="I21" s="183"/>
-      <c r="J21" s="184"/>
+      <c r="G21" s="210"/>
+      <c r="H21" s="211"/>
+      <c r="I21" s="175"/>
+      <c r="J21" s="176"/>
       <c r="K21" s="64"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4316,10 +4313,10 @@
       <c r="D22" s="63"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="189"/>
-      <c r="H22" s="190"/>
-      <c r="I22" s="183"/>
-      <c r="J22" s="184"/>
+      <c r="G22" s="210"/>
+      <c r="H22" s="211"/>
+      <c r="I22" s="175"/>
+      <c r="J22" s="176"/>
       <c r="K22" s="64"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4338,10 +4335,10 @@
       <c r="D23" s="63"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="189"/>
-      <c r="H23" s="190"/>
-      <c r="I23" s="183"/>
-      <c r="J23" s="184"/>
+      <c r="G23" s="210"/>
+      <c r="H23" s="211"/>
+      <c r="I23" s="175"/>
+      <c r="J23" s="176"/>
       <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4360,10 +4357,10 @@
       <c r="D24" s="63"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="189"/>
-      <c r="H24" s="190"/>
-      <c r="I24" s="183"/>
-      <c r="J24" s="184"/>
+      <c r="G24" s="210"/>
+      <c r="H24" s="211"/>
+      <c r="I24" s="175"/>
+      <c r="J24" s="176"/>
       <c r="K24" s="64"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4382,10 +4379,10 @@
       <c r="D25" s="63"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="189"/>
-      <c r="H25" s="190"/>
-      <c r="I25" s="183"/>
-      <c r="J25" s="184"/>
+      <c r="G25" s="210"/>
+      <c r="H25" s="211"/>
+      <c r="I25" s="175"/>
+      <c r="J25" s="176"/>
       <c r="K25" s="64"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4404,10 +4401,10 @@
       <c r="D26" s="63"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="189"/>
-      <c r="H26" s="190"/>
-      <c r="I26" s="183"/>
-      <c r="J26" s="184"/>
+      <c r="G26" s="210"/>
+      <c r="H26" s="211"/>
+      <c r="I26" s="175"/>
+      <c r="J26" s="176"/>
       <c r="K26" s="64"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4426,10 +4423,10 @@
       <c r="D27" s="63"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="189"/>
-      <c r="H27" s="190"/>
-      <c r="I27" s="183"/>
-      <c r="J27" s="184"/>
+      <c r="G27" s="210"/>
+      <c r="H27" s="211"/>
+      <c r="I27" s="175"/>
+      <c r="J27" s="176"/>
       <c r="K27" s="64"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4448,10 +4445,10 @@
       <c r="D28" s="63"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="189"/>
-      <c r="H28" s="190"/>
-      <c r="I28" s="183"/>
-      <c r="J28" s="184"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="211"/>
+      <c r="I28" s="175"/>
+      <c r="J28" s="176"/>
       <c r="K28" s="64"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4470,10 +4467,10 @@
       <c r="D29" s="63"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="189"/>
-      <c r="H29" s="190"/>
-      <c r="I29" s="183"/>
-      <c r="J29" s="184"/>
+      <c r="G29" s="210"/>
+      <c r="H29" s="211"/>
+      <c r="I29" s="175"/>
+      <c r="J29" s="176"/>
       <c r="K29" s="64"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4492,10 +4489,10 @@
       <c r="D30" s="63"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="189"/>
-      <c r="H30" s="190"/>
-      <c r="I30" s="183"/>
-      <c r="J30" s="184"/>
+      <c r="G30" s="210"/>
+      <c r="H30" s="211"/>
+      <c r="I30" s="175"/>
+      <c r="J30" s="176"/>
       <c r="K30" s="64"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4514,10 +4511,10 @@
       <c r="D31" s="63"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="190"/>
-      <c r="I31" s="183"/>
-      <c r="J31" s="184"/>
+      <c r="G31" s="210"/>
+      <c r="H31" s="211"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="176"/>
       <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4536,10 +4533,10 @@
       <c r="D32" s="63"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="189"/>
-      <c r="H32" s="190"/>
-      <c r="I32" s="183"/>
-      <c r="J32" s="184"/>
+      <c r="G32" s="210"/>
+      <c r="H32" s="211"/>
+      <c r="I32" s="175"/>
+      <c r="J32" s="176"/>
       <c r="K32" s="64"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4558,10 +4555,10 @@
       <c r="D33" s="63"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="189"/>
-      <c r="H33" s="190"/>
-      <c r="I33" s="183"/>
-      <c r="J33" s="184"/>
+      <c r="G33" s="210"/>
+      <c r="H33" s="211"/>
+      <c r="I33" s="175"/>
+      <c r="J33" s="176"/>
       <c r="K33" s="64"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4580,10 +4577,10 @@
       <c r="D34" s="63"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="189"/>
-      <c r="H34" s="190"/>
-      <c r="I34" s="183"/>
-      <c r="J34" s="184"/>
+      <c r="G34" s="210"/>
+      <c r="H34" s="211"/>
+      <c r="I34" s="175"/>
+      <c r="J34" s="176"/>
       <c r="K34" s="64"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4602,10 +4599,10 @@
       <c r="D35" s="63"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="189"/>
-      <c r="H35" s="190"/>
-      <c r="I35" s="183"/>
-      <c r="J35" s="184"/>
+      <c r="G35" s="210"/>
+      <c r="H35" s="211"/>
+      <c r="I35" s="175"/>
+      <c r="J35" s="176"/>
       <c r="K35" s="64"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4624,10 +4621,10 @@
       <c r="D36" s="63"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="189"/>
-      <c r="H36" s="190"/>
-      <c r="I36" s="183"/>
-      <c r="J36" s="184"/>
+      <c r="G36" s="210"/>
+      <c r="H36" s="211"/>
+      <c r="I36" s="175"/>
+      <c r="J36" s="176"/>
       <c r="K36" s="64"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4646,10 +4643,10 @@
       <c r="D37" s="63"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="189"/>
-      <c r="H37" s="190"/>
-      <c r="I37" s="183"/>
-      <c r="J37" s="184"/>
+      <c r="G37" s="210"/>
+      <c r="H37" s="211"/>
+      <c r="I37" s="175"/>
+      <c r="J37" s="176"/>
       <c r="K37" s="64"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4668,10 +4665,10 @@
       <c r="D38" s="63"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="189"/>
-      <c r="H38" s="190"/>
-      <c r="I38" s="183"/>
-      <c r="J38" s="184"/>
+      <c r="G38" s="210"/>
+      <c r="H38" s="211"/>
+      <c r="I38" s="175"/>
+      <c r="J38" s="176"/>
       <c r="K38" s="64"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4690,10 +4687,10 @@
       <c r="D39" s="63"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="189"/>
-      <c r="H39" s="190"/>
-      <c r="I39" s="183"/>
-      <c r="J39" s="184"/>
+      <c r="G39" s="210"/>
+      <c r="H39" s="211"/>
+      <c r="I39" s="175"/>
+      <c r="J39" s="176"/>
       <c r="K39" s="64"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4712,18 +4709,18 @@
       <c r="D40" s="63"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="183"/>
-      <c r="J40" s="184"/>
+      <c r="G40" s="213"/>
+      <c r="H40" s="213"/>
+      <c r="I40" s="175"/>
+      <c r="J40" s="176"/>
       <c r="K40" s="64"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="173" t="s">
+      <c r="A41" s="216" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="174"/>
-      <c r="C41" s="174"/>
+      <c r="B41" s="217"/>
+      <c r="C41" s="217"/>
       <c r="D41" s="65" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4736,27 +4733,27 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="191" t="e">
+      <c r="G41" s="214" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="192"/>
-      <c r="I41" s="225" t="e">
+      <c r="H41" s="215"/>
+      <c r="I41" s="177" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="226"/>
+      <c r="J41" s="178"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="175" t="s">
+      <c r="A42" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="176"/>
-      <c r="C42" s="176"/>
+      <c r="B42" s="219"/>
+      <c r="C42" s="219"/>
       <c r="D42" s="66">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4769,27 +4766,27 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="187">
+      <c r="G42" s="225">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="188"/>
-      <c r="I42" s="223">
+      <c r="H42" s="226"/>
+      <c r="I42" s="173">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="224"/>
+      <c r="J42" s="174"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="221" t="s">
+      <c r="A43" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="222"/>
-      <c r="C43" s="222"/>
+      <c r="B43" s="184"/>
+      <c r="C43" s="184"/>
       <c r="D43" s="67">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4802,16 +4799,16 @@
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="217">
+      <c r="G43" s="179">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="218"/>
-      <c r="I43" s="219">
+      <c r="H43" s="180"/>
+      <c r="I43" s="181">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="220"/>
+      <c r="J43" s="182"/>
       <c r="K43" s="69">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4821,8 +4818,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="171"/>
-      <c r="C44" s="171"/>
+      <c r="B44" s="151"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -4839,8 +4836,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="152"/>
+      <c r="C45" s="152"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -4849,11 +4846,11 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="156" t="s">
+      <c r="A46" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="156"/>
-      <c r="C46" s="156"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
@@ -4866,11 +4863,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="156" t="s">
+      <c r="A47" s="134" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="156"/>
-      <c r="C47" s="156"/>
+      <c r="B47" s="134"/>
+      <c r="C47" s="134"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -4925,52 +4922,38 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="G7:H10"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="G39:H39"/>
@@ -4987,38 +4970,52 @@
     <mergeCell ref="G36:H36"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
@@ -5074,35 +5071,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5123,18 +5120,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145">
+      <c r="B4" s="163">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="177">
+      <c r="C4" s="220">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="178"/>
+      <c r="D4" s="209"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5152,25 +5149,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="179">
+      <c r="J4" s="221">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="180"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149">
+      <c r="B5" s="167">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="150">
+      <c r="C5" s="168">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="151"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5188,11 +5185,11 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="195">
+      <c r="J5" s="185">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="196"/>
+      <c r="K5" s="186"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="227" t="s">
@@ -5201,66 +5198,66 @@
       <c r="B6" s="228"/>
       <c r="C6" s="229"/>
       <c r="D6" s="230"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="155"/>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154"/>
+      <c r="G6" s="172"/>
       <c r="H6" s="71"/>
-      <c r="I6" s="197"/>
-      <c r="J6" s="198"/>
-      <c r="K6" s="204"/>
+      <c r="I6" s="187"/>
+      <c r="J6" s="188"/>
+      <c r="K6" s="195"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="216" t="s">
+      <c r="A7" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="208" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="231"/>
       <c r="F7" s="231"/>
       <c r="G7" s="232"/>
-      <c r="H7" s="204" t="s">
+      <c r="H7" s="195" t="s">
         <v>126</v>
       </c>
-      <c r="I7" s="199"/>
-      <c r="J7" s="200"/>
-      <c r="K7" s="205"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="196"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="199"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="200"/>
+      <c r="A8" s="189"/>
+      <c r="B8" s="190"/>
+      <c r="C8" s="190"/>
       <c r="D8" s="235" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="237" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="237" t="s">
+      <c r="F8" s="237" t="s">
         <v>141</v>
-      </c>
-      <c r="F8" s="237" t="s">
-        <v>142</v>
       </c>
       <c r="G8" s="239" t="s">
         <v>128</v>
       </c>
-      <c r="H8" s="205"/>
-      <c r="I8" s="199"/>
-      <c r="J8" s="200"/>
-      <c r="K8" s="205"/>
+      <c r="H8" s="196"/>
+      <c r="I8" s="189"/>
+      <c r="J8" s="190"/>
+      <c r="K8" s="196"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="199"/>
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
+      <c r="A9" s="189"/>
+      <c r="B9" s="190"/>
+      <c r="C9" s="190"/>
       <c r="D9" s="236"/>
       <c r="E9" s="238"/>
       <c r="F9" s="238"/>
       <c r="G9" s="240"/>
-      <c r="H9" s="206"/>
-      <c r="I9" s="199"/>
-      <c r="J9" s="200"/>
-      <c r="K9" s="205"/>
+      <c r="H9" s="197"/>
+      <c r="I9" s="189"/>
+      <c r="J9" s="190"/>
+      <c r="K9" s="196"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="120">
@@ -5280,9 +5277,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="73"/>
       <c r="H10" s="74"/>
-      <c r="I10" s="199"/>
-      <c r="J10" s="200"/>
-      <c r="K10" s="205"/>
+      <c r="I10" s="189"/>
+      <c r="J10" s="190"/>
+      <c r="K10" s="196"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="123">
@@ -5302,9 +5299,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="76"/>
       <c r="H11" s="77"/>
-      <c r="I11" s="199"/>
-      <c r="J11" s="200"/>
-      <c r="K11" s="205"/>
+      <c r="I11" s="189"/>
+      <c r="J11" s="190"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="123">
@@ -5324,9 +5321,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="76"/>
       <c r="H12" s="77"/>
-      <c r="I12" s="199"/>
-      <c r="J12" s="200"/>
-      <c r="K12" s="205"/>
+      <c r="I12" s="189"/>
+      <c r="J12" s="190"/>
+      <c r="K12" s="196"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="123">
@@ -5346,9 +5343,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="73"/>
       <c r="H13" s="77"/>
-      <c r="I13" s="199"/>
-      <c r="J13" s="200"/>
-      <c r="K13" s="205"/>
+      <c r="I13" s="189"/>
+      <c r="J13" s="190"/>
+      <c r="K13" s="196"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="123">
@@ -5368,9 +5365,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="76"/>
       <c r="H14" s="77"/>
-      <c r="I14" s="199"/>
-      <c r="J14" s="200"/>
-      <c r="K14" s="205"/>
+      <c r="I14" s="189"/>
+      <c r="J14" s="190"/>
+      <c r="K14" s="196"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="123">
@@ -5390,9 +5387,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="76"/>
       <c r="H15" s="77"/>
-      <c r="I15" s="199"/>
-      <c r="J15" s="200"/>
-      <c r="K15" s="205"/>
+      <c r="I15" s="189"/>
+      <c r="J15" s="190"/>
+      <c r="K15" s="196"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="123">
@@ -5412,9 +5409,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="76"/>
       <c r="H16" s="77"/>
-      <c r="I16" s="199"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="205"/>
+      <c r="I16" s="189"/>
+      <c r="J16" s="190"/>
+      <c r="K16" s="196"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="123">
@@ -5434,9 +5431,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="76"/>
       <c r="H17" s="77"/>
-      <c r="I17" s="199"/>
-      <c r="J17" s="200"/>
-      <c r="K17" s="205"/>
+      <c r="I17" s="189"/>
+      <c r="J17" s="190"/>
+      <c r="K17" s="196"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="123">
@@ -5456,9 +5453,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="76"/>
       <c r="H18" s="77"/>
-      <c r="I18" s="199"/>
-      <c r="J18" s="200"/>
-      <c r="K18" s="205"/>
+      <c r="I18" s="189"/>
+      <c r="J18" s="190"/>
+      <c r="K18" s="196"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="123">
@@ -5478,9 +5475,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="76"/>
       <c r="H19" s="77"/>
-      <c r="I19" s="199"/>
-      <c r="J19" s="200"/>
-      <c r="K19" s="205"/>
+      <c r="I19" s="189"/>
+      <c r="J19" s="190"/>
+      <c r="K19" s="196"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
@@ -5500,9 +5497,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="76"/>
       <c r="H20" s="77"/>
-      <c r="I20" s="199"/>
-      <c r="J20" s="200"/>
-      <c r="K20" s="205"/>
+      <c r="I20" s="189"/>
+      <c r="J20" s="190"/>
+      <c r="K20" s="196"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="123">
@@ -5522,9 +5519,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="76"/>
       <c r="H21" s="77"/>
-      <c r="I21" s="199"/>
-      <c r="J21" s="200"/>
-      <c r="K21" s="205"/>
+      <c r="I21" s="189"/>
+      <c r="J21" s="190"/>
+      <c r="K21" s="196"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="123">
@@ -5544,9 +5541,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="76"/>
       <c r="H22" s="77"/>
-      <c r="I22" s="199"/>
-      <c r="J22" s="200"/>
-      <c r="K22" s="205"/>
+      <c r="I22" s="189"/>
+      <c r="J22" s="190"/>
+      <c r="K22" s="196"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="123">
@@ -5566,9 +5563,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="76"/>
       <c r="H23" s="77"/>
-      <c r="I23" s="199"/>
-      <c r="J23" s="200"/>
-      <c r="K23" s="205"/>
+      <c r="I23" s="189"/>
+      <c r="J23" s="190"/>
+      <c r="K23" s="196"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="123">
@@ -5588,9 +5585,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="76"/>
       <c r="H24" s="77"/>
-      <c r="I24" s="199"/>
-      <c r="J24" s="200"/>
-      <c r="K24" s="205"/>
+      <c r="I24" s="189"/>
+      <c r="J24" s="190"/>
+      <c r="K24" s="196"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="123">
@@ -5610,9 +5607,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="76"/>
       <c r="H25" s="77"/>
-      <c r="I25" s="199"/>
-      <c r="J25" s="200"/>
-      <c r="K25" s="205"/>
+      <c r="I25" s="189"/>
+      <c r="J25" s="190"/>
+      <c r="K25" s="196"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="123">
@@ -5632,9 +5629,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="76"/>
       <c r="H26" s="77"/>
-      <c r="I26" s="199"/>
-      <c r="J26" s="200"/>
-      <c r="K26" s="205"/>
+      <c r="I26" s="189"/>
+      <c r="J26" s="190"/>
+      <c r="K26" s="196"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="123">
@@ -5654,9 +5651,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="76"/>
       <c r="H27" s="77"/>
-      <c r="I27" s="199"/>
-      <c r="J27" s="200"/>
-      <c r="K27" s="205"/>
+      <c r="I27" s="189"/>
+      <c r="J27" s="190"/>
+      <c r="K27" s="196"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="123">
@@ -5676,9 +5673,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="76"/>
       <c r="H28" s="77"/>
-      <c r="I28" s="199"/>
-      <c r="J28" s="200"/>
-      <c r="K28" s="205"/>
+      <c r="I28" s="189"/>
+      <c r="J28" s="190"/>
+      <c r="K28" s="196"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="123">
@@ -5698,9 +5695,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="76"/>
       <c r="H29" s="77"/>
-      <c r="I29" s="199"/>
-      <c r="J29" s="200"/>
-      <c r="K29" s="205"/>
+      <c r="I29" s="189"/>
+      <c r="J29" s="190"/>
+      <c r="K29" s="196"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
@@ -5720,9 +5717,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="76"/>
       <c r="H30" s="77"/>
-      <c r="I30" s="199"/>
-      <c r="J30" s="200"/>
-      <c r="K30" s="205"/>
+      <c r="I30" s="189"/>
+      <c r="J30" s="190"/>
+      <c r="K30" s="196"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="123">
@@ -5742,9 +5739,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="76"/>
       <c r="H31" s="77"/>
-      <c r="I31" s="199"/>
-      <c r="J31" s="200"/>
-      <c r="K31" s="205"/>
+      <c r="I31" s="189"/>
+      <c r="J31" s="190"/>
+      <c r="K31" s="196"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="123">
@@ -5764,9 +5761,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="76"/>
       <c r="H32" s="77"/>
-      <c r="I32" s="199"/>
-      <c r="J32" s="200"/>
-      <c r="K32" s="205"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="190"/>
+      <c r="K32" s="196"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="123">
@@ -5786,9 +5783,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="76"/>
       <c r="H33" s="77"/>
-      <c r="I33" s="199"/>
-      <c r="J33" s="200"/>
-      <c r="K33" s="205"/>
+      <c r="I33" s="189"/>
+      <c r="J33" s="190"/>
+      <c r="K33" s="196"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="123">
@@ -5808,9 +5805,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="76"/>
       <c r="H34" s="77"/>
-      <c r="I34" s="199"/>
-      <c r="J34" s="200"/>
-      <c r="K34" s="205"/>
+      <c r="I34" s="189"/>
+      <c r="J34" s="190"/>
+      <c r="K34" s="196"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="123">
@@ -5830,9 +5827,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="76"/>
       <c r="H35" s="77"/>
-      <c r="I35" s="199"/>
-      <c r="J35" s="200"/>
-      <c r="K35" s="205"/>
+      <c r="I35" s="189"/>
+      <c r="J35" s="190"/>
+      <c r="K35" s="196"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="123">
@@ -5852,9 +5849,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="76"/>
       <c r="H36" s="77"/>
-      <c r="I36" s="199"/>
-      <c r="J36" s="200"/>
-      <c r="K36" s="205"/>
+      <c r="I36" s="189"/>
+      <c r="J36" s="190"/>
+      <c r="K36" s="196"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="123">
@@ -5874,9 +5871,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="76"/>
       <c r="H37" s="77"/>
-      <c r="I37" s="199"/>
-      <c r="J37" s="200"/>
-      <c r="K37" s="205"/>
+      <c r="I37" s="189"/>
+      <c r="J37" s="190"/>
+      <c r="K37" s="196"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="123">
@@ -5896,9 +5893,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="76"/>
       <c r="H38" s="77"/>
-      <c r="I38" s="199"/>
-      <c r="J38" s="200"/>
-      <c r="K38" s="205"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="190"/>
+      <c r="K38" s="196"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="130">
@@ -5918,9 +5915,9 @@
       <c r="F39" s="26"/>
       <c r="G39" s="76"/>
       <c r="H39" s="77"/>
-      <c r="I39" s="199"/>
-      <c r="J39" s="200"/>
-      <c r="K39" s="205"/>
+      <c r="I39" s="189"/>
+      <c r="J39" s="190"/>
+      <c r="K39" s="196"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="233" t="s">
@@ -5948,16 +5945,16 @@
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="200"/>
-      <c r="J40" s="200"/>
-      <c r="K40" s="205"/>
+      <c r="I40" s="190"/>
+      <c r="J40" s="190"/>
+      <c r="K40" s="196"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="175" t="s">
+      <c r="A41" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="176"/>
-      <c r="C41" s="176"/>
+      <c r="B41" s="219"/>
+      <c r="C41" s="219"/>
       <c r="D41" s="80">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -5978,16 +5975,16 @@
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="200"/>
-      <c r="J41" s="200"/>
-      <c r="K41" s="205"/>
+      <c r="I41" s="190"/>
+      <c r="J41" s="190"/>
+      <c r="K41" s="196"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="221" t="s">
+      <c r="A42" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="222"/>
-      <c r="C42" s="222"/>
+      <c r="B42" s="184"/>
+      <c r="C42" s="184"/>
       <c r="D42" s="82">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -6008,16 +6005,16 @@
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="203"/>
-      <c r="J42" s="203"/>
-      <c r="K42" s="206"/>
+      <c r="I42" s="194"/>
+      <c r="J42" s="194"/>
+      <c r="K42" s="197"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="171"/>
-      <c r="C43" s="171"/>
+      <c r="B43" s="151"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -6034,8 +6031,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="172"/>
-      <c r="C44" s="172"/>
+      <c r="B44" s="152"/>
+      <c r="C44" s="152"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -6044,11 +6041,11 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="156" t="s">
+      <c r="A45" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="156"/>
-      <c r="C45" s="156"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="134"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
@@ -6061,11 +6058,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="156" t="s">
+      <c r="A46" s="134" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="156"/>
-      <c r="C46" s="156"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -6090,6 +6087,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="I6:K42"/>
     <mergeCell ref="H7:H9"/>
@@ -6106,15 +6112,6 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
@@ -6167,15 +6164,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="291" t="s">
+      <c r="A1" s="242" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-      <c r="G1" s="293"/>
+      <c r="B1" s="243"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
+      <c r="F1" s="243"/>
+      <c r="G1" s="244"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -6189,37 +6186,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="299" t="s">
+      <c r="A3" s="253" t="s">
         <v>137</v>
       </c>
-      <c r="B3" s="300"/>
-      <c r="C3" s="300"/>
-      <c r="D3" s="300"/>
-      <c r="E3" s="300"/>
-      <c r="F3" s="300"/>
-      <c r="G3" s="301"/>
+      <c r="B3" s="254"/>
+      <c r="C3" s="254"/>
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="255"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="199" t="s">
+      <c r="A4" s="189" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="200"/>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="205"/>
+      <c r="B4" s="190"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="196"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="294" t="s">
+      <c r="A5" s="245" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="295"/>
-      <c r="C5" s="295"/>
-      <c r="D5" s="295"/>
-      <c r="E5" s="295"/>
-      <c r="F5" s="295"/>
-      <c r="G5" s="296"/>
+      <c r="B5" s="246"/>
+      <c r="C5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="247"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -6231,14 +6228,15 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="259" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="261"/>
-      <c r="F6" s="297" t="s">
+      <c r="D6" s="248">
+        <f>Page1!H4</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="249"/>
+      <c r="F6" s="250" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="282">
+      <c r="G6" s="251">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6251,13 +6249,13 @@
       <c r="C7" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="259">
+      <c r="D7" s="248">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="261"/>
-      <c r="F7" s="297"/>
-      <c r="G7" s="298"/>
+      <c r="E7" s="249"/>
+      <c r="F7" s="250"/>
+      <c r="G7" s="252"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -6270,15 +6268,15 @@
       <c r="C8" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="297">
+      <c r="D8" s="250">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="297"/>
-      <c r="F8" s="279" t="s">
+      <c r="E8" s="250"/>
+      <c r="F8" s="265" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="282">
+      <c r="G8" s="251">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6291,15 +6289,15 @@
         <f>Page1!G44</f>
         <v>461309100</v>
       </c>
-      <c r="C9" s="279" t="s">
+      <c r="C9" s="265" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="285" t="s">
+      <c r="D9" s="270" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="286"/>
-      <c r="F9" s="280"/>
-      <c r="G9" s="283"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="266"/>
+      <c r="G9" s="268"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -6309,34 +6307,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="281"/>
-      <c r="D10" s="287"/>
-      <c r="E10" s="288"/>
-      <c r="F10" s="281"/>
-      <c r="G10" s="284"/>
+      <c r="C10" s="267"/>
+      <c r="D10" s="272"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="267"/>
+      <c r="G10" s="269"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="302" t="s">
+      <c r="A11" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="304" t="s">
+      <c r="B11" s="258" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="306" t="s">
+      <c r="C11" s="260" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="307"/>
-      <c r="E11" s="308"/>
-      <c r="F11" s="304" t="s">
+      <c r="D11" s="261"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="258" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="309" t="s">
+      <c r="G11" s="263" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="303"/>
-      <c r="B12" s="305"/>
+      <c r="A12" s="257"/>
+      <c r="B12" s="259"/>
       <c r="C12" s="99" t="s">
         <v>60</v>
       </c>
@@ -6346,8 +6344,8 @@
       <c r="E12" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="305"/>
-      <c r="G12" s="310"/>
+      <c r="F12" s="259"/>
+      <c r="G12" s="264"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -6441,7 +6439,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="289"/>
+      <c r="G16" s="274"/>
     </row>
     <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
@@ -6463,7 +6461,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="289"/>
+      <c r="G17" s="274"/>
     </row>
     <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104" t="s">
@@ -6485,7 +6483,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="289"/>
+      <c r="G18" s="274"/>
     </row>
     <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104" t="s">
@@ -6507,7 +6505,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="289"/>
+      <c r="G19" s="274"/>
     </row>
     <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
@@ -6529,7 +6527,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="289"/>
+      <c r="G20" s="274"/>
     </row>
     <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
@@ -6551,7 +6549,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="289"/>
+      <c r="G21" s="274"/>
     </row>
     <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="104" t="s">
@@ -6573,7 +6571,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="138"/>
+      <c r="G22" s="156"/>
     </row>
     <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -6673,26 +6671,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="273" t="s">
+      <c r="A27" s="275" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="274"/>
-      <c r="C27" s="274"/>
-      <c r="D27" s="274"/>
-      <c r="E27" s="274"/>
-      <c r="F27" s="274"/>
-      <c r="G27" s="275"/>
+      <c r="B27" s="276"/>
+      <c r="C27" s="276"/>
+      <c r="D27" s="276"/>
+      <c r="E27" s="276"/>
+      <c r="F27" s="276"/>
+      <c r="G27" s="277"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="257" t="s">
+      <c r="A28" s="278" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="258"/>
-      <c r="C28" s="276" t="s">
+      <c r="B28" s="279"/>
+      <c r="C28" s="280" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="277"/>
-      <c r="E28" s="278"/>
+      <c r="D28" s="281"/>
+      <c r="E28" s="282"/>
       <c r="F28" s="113" t="s">
         <v>92</v>
       </c>
@@ -6701,15 +6699,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="262" t="s">
+      <c r="A29" s="283" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="261"/>
-      <c r="C29" s="267" t="s">
+      <c r="B29" s="249"/>
+      <c r="C29" s="284" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="268"/>
-      <c r="E29" s="269"/>
+      <c r="D29" s="285"/>
+      <c r="E29" s="286"/>
       <c r="F29" s="66" t="s">
         <v>92</v>
       </c>
@@ -6718,15 +6716,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="262" t="s">
+      <c r="A30" s="283" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="261"/>
-      <c r="C30" s="267" t="s">
+      <c r="B30" s="249"/>
+      <c r="C30" s="284" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="268"/>
-      <c r="E30" s="269"/>
+      <c r="D30" s="285"/>
+      <c r="E30" s="286"/>
       <c r="F30" s="66" t="s">
         <v>92</v>
       </c>
@@ -6735,15 +6733,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="262" t="s">
+      <c r="A31" s="283" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="261"/>
-      <c r="C31" s="267" t="s">
+      <c r="B31" s="249"/>
+      <c r="C31" s="284" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="268"/>
-      <c r="E31" s="269"/>
+      <c r="D31" s="285"/>
+      <c r="E31" s="286"/>
       <c r="F31" s="66" t="s">
         <v>92</v>
       </c>
@@ -6752,15 +6750,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="262" t="s">
+      <c r="A32" s="283" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="261"/>
-      <c r="C32" s="267" t="s">
+      <c r="B32" s="249"/>
+      <c r="C32" s="284" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="268"/>
-      <c r="E32" s="269"/>
+      <c r="D32" s="285"/>
+      <c r="E32" s="286"/>
       <c r="F32" s="66" t="s">
         <v>92</v>
       </c>
@@ -6769,15 +6767,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="262" t="s">
+      <c r="A33" s="283" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="261"/>
-      <c r="C33" s="267" t="s">
+      <c r="B33" s="249"/>
+      <c r="C33" s="284" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="268"/>
-      <c r="E33" s="269"/>
+      <c r="D33" s="285"/>
+      <c r="E33" s="286"/>
       <c r="F33" s="66" t="s">
         <v>92</v>
       </c>
@@ -6786,15 +6784,15 @@
       </c>
     </row>
     <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="166" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="149"/>
-      <c r="C34" s="270" t="s">
+      <c r="B34" s="167"/>
+      <c r="C34" s="289" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="271"/>
-      <c r="E34" s="272"/>
+      <c r="D34" s="290"/>
+      <c r="E34" s="291"/>
       <c r="F34" s="114" t="s">
         <v>92</v>
       </c>
@@ -6803,26 +6801,26 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="273" t="s">
+      <c r="A35" s="275" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="274"/>
-      <c r="C35" s="274"/>
-      <c r="D35" s="274"/>
-      <c r="E35" s="274"/>
-      <c r="F35" s="274"/>
-      <c r="G35" s="275"/>
+      <c r="B35" s="276"/>
+      <c r="C35" s="276"/>
+      <c r="D35" s="276"/>
+      <c r="E35" s="276"/>
+      <c r="F35" s="276"/>
+      <c r="G35" s="277"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="144" t="s">
+      <c r="A36" s="162" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="145"/>
-      <c r="C36" s="265" t="s">
+      <c r="B36" s="163"/>
+      <c r="C36" s="287" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="266"/>
-      <c r="E36" s="145"/>
+      <c r="D36" s="288"/>
+      <c r="E36" s="163"/>
       <c r="F36" s="10" t="s">
         <v>92</v>
       </c>
@@ -6831,15 +6829,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="257" t="s">
+      <c r="A37" s="278" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="258"/>
-      <c r="C37" s="259" t="s">
+      <c r="B37" s="279"/>
+      <c r="C37" s="248" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="260"/>
-      <c r="E37" s="261"/>
+      <c r="D37" s="292"/>
+      <c r="E37" s="249"/>
       <c r="F37" s="106" t="s">
         <v>92</v>
       </c>
@@ -6848,15 +6846,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="262" t="s">
+      <c r="A38" s="283" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="261"/>
-      <c r="C38" s="259" t="s">
+      <c r="B38" s="249"/>
+      <c r="C38" s="248" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="260"/>
-      <c r="E38" s="261"/>
+      <c r="D38" s="292"/>
+      <c r="E38" s="249"/>
       <c r="F38" s="106" t="s">
         <v>92</v>
       </c>
@@ -6865,15 +6863,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="148" t="s">
+      <c r="A39" s="166" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="149"/>
-      <c r="C39" s="263" t="s">
+      <c r="B39" s="167"/>
+      <c r="C39" s="293" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="264"/>
-      <c r="E39" s="149"/>
+      <c r="D39" s="294"/>
+      <c r="E39" s="167"/>
       <c r="F39" s="1" t="s">
         <v>92</v>
       </c>
@@ -6882,50 +6880,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="243" t="s">
+      <c r="A40" s="297" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="244"/>
-      <c r="C40" s="245" t="s">
+      <c r="B40" s="298"/>
+      <c r="C40" s="299" t="s">
         <v>134</v>
       </c>
-      <c r="D40" s="246"/>
-      <c r="E40" s="247"/>
-      <c r="F40" s="245" t="s">
+      <c r="D40" s="300"/>
+      <c r="E40" s="301"/>
+      <c r="F40" s="299" t="s">
         <v>135</v>
       </c>
-      <c r="G40" s="247"/>
+      <c r="G40" s="301"/>
     </row>
     <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="248"/>
-      <c r="B41" s="249"/>
-      <c r="C41" s="199"/>
-      <c r="D41" s="200"/>
-      <c r="E41" s="205"/>
-      <c r="F41" s="252"/>
-      <c r="G41" s="253"/>
+      <c r="A41" s="302"/>
+      <c r="B41" s="303"/>
+      <c r="C41" s="189"/>
+      <c r="D41" s="190"/>
+      <c r="E41" s="196"/>
+      <c r="F41" s="306"/>
+      <c r="G41" s="307"/>
     </row>
     <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="250"/>
-      <c r="B42" s="251"/>
-      <c r="C42" s="254" t="s">
+      <c r="A42" s="304"/>
+      <c r="B42" s="305"/>
+      <c r="C42" s="308" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="255"/>
-      <c r="E42" s="256"/>
-      <c r="F42" s="254" t="s">
+      <c r="D42" s="309"/>
+      <c r="E42" s="310"/>
+      <c r="F42" s="308" t="s">
         <v>136</v>
       </c>
-      <c r="G42" s="256"/>
+      <c r="G42" s="310"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="241"/>
-      <c r="F43" s="241"/>
-      <c r="G43" s="241"/>
+      <c r="E43" s="295"/>
+      <c r="F43" s="295"/>
+      <c r="G43" s="295"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -6934,24 +6932,63 @@
       <c r="B44" s="116"/>
       <c r="C44" s="118"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="242"/>
-      <c r="F44" s="242"/>
-      <c r="G44" s="242"/>
+      <c r="E44" s="296"/>
+      <c r="F44" s="296"/>
+      <c r="G44" s="296"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="290" t="s">
+      <c r="A46" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="290"/>
+      <c r="B46" s="241"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="290" t="s">
+      <c r="A47" s="241" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="290"/>
+      <c r="B47" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="G15:G22"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:G1"/>
@@ -6968,45 +7005,6 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="G15:G22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F42:G42"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/UC-18gsm-250W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-250W-BFQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8013345-787B-4F42-ADEC-3FA841D92683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12BB227-7190-4EF2-A23A-918D5284C1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1443,7 +1443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="311">
+  <cellXfs count="312">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2399,20 +2399,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6894,27 +6897,27 @@
       </c>
       <c r="G40" s="301"/>
     </row>
-    <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" s="86" customFormat="1" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="302"/>
       <c r="B41" s="303"/>
-      <c r="C41" s="189"/>
-      <c r="D41" s="190"/>
-      <c r="E41" s="196"/>
+      <c r="C41" s="306"/>
+      <c r="D41" s="307"/>
+      <c r="E41" s="308"/>
       <c r="F41" s="306"/>
-      <c r="G41" s="307"/>
-    </row>
-    <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G41" s="308"/>
+    </row>
+    <row r="42" spans="1:7" s="86" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="304"/>
       <c r="B42" s="305"/>
-      <c r="C42" s="308" t="s">
+      <c r="C42" s="309" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="309"/>
-      <c r="E42" s="310"/>
-      <c r="F42" s="308" t="s">
+      <c r="D42" s="310"/>
+      <c r="E42" s="311"/>
+      <c r="F42" s="309" t="s">
         <v>136</v>
       </c>
-      <c r="G42" s="310"/>
+      <c r="G42" s="311"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
